--- a/Excel/EquipConfig.xlsx
+++ b/Excel/EquipConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255" activeTab="3"/>
+    <workbookView windowWidth="28800" windowHeight="12375" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="随机装备" sheetId="3" r:id="rId1"/>
@@ -143,7 +143,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21406" uniqueCount="4004">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21430" uniqueCount="4020">
   <si>
     <t>_id</t>
   </si>
@@ -11701,6 +11701,18 @@
     <t>1800,1800,1800,1800,80,400</t>
   </si>
   <si>
+    <t>斗笠二五阶</t>
+  </si>
+  <si>
+    <t>2400,2400,2400,2400,90,600</t>
+  </si>
+  <si>
+    <t>斗笠二六阶</t>
+  </si>
+  <si>
+    <t>3000,3000,3000,3000,100,800</t>
+  </si>
+  <si>
     <t>护盾一阶</t>
   </si>
   <si>
@@ -11851,6 +11863,18 @@
     <t>1800,1800,1800,40,80,400</t>
   </si>
   <si>
+    <t>护盾二五阶</t>
+  </si>
+  <si>
+    <t>2400,2400,2400,50,100,600</t>
+  </si>
+  <si>
+    <t>护盾二六阶</t>
+  </si>
+  <si>
+    <t>3000,3000,3000,60,120,800</t>
+  </si>
+  <si>
     <t>神符一阶</t>
   </si>
   <si>
@@ -12001,6 +12025,18 @@
     <t>180,80,1800,1800,1800,80</t>
   </si>
   <si>
+    <t>神符二五阶</t>
+  </si>
+  <si>
+    <t>240,90,2400,2400,2400,100</t>
+  </si>
+  <si>
+    <t>神符二六阶</t>
+  </si>
+  <si>
+    <t>300,100,3000,3000,3000,120</t>
+  </si>
+  <si>
     <t>魔石一阶</t>
   </si>
   <si>
@@ -12155,6 +12191,18 @@
   </si>
   <si>
     <t>80,1800,6,120,120,400</t>
+  </si>
+  <si>
+    <t>魔石二五阶</t>
+  </si>
+  <si>
+    <t>90,2400,6,160,160,600</t>
+  </si>
+  <si>
+    <t>魔石二六阶</t>
+  </si>
+  <si>
+    <t>100,3000,6,200,200,800</t>
   </si>
 </sst>
 </file>
@@ -85533,7 +85581,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:P125"/>
+  <dimension ref="A1:P131"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9" style="2"/>
@@ -87101,36 +87149,77 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" s="2" customFormat="1" customHeight="1" spans="9:9">
-      <c r="I38" s="9"/>
+    <row r="38" s="2" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C38" s="2">
+        <v>125</v>
+      </c>
+      <c r="D38" s="2">
+        <v>25</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>3852</v>
+      </c>
+      <c r="F38" s="2">
+        <v>11</v>
+      </c>
+      <c r="G38" s="2">
+        <v>11</v>
+      </c>
+      <c r="H38" s="20" t="s">
+        <v>3848</v>
+      </c>
+      <c r="I38" s="22" t="s">
+        <v>3853</v>
+      </c>
+      <c r="J38" s="2">
+        <v>-1</v>
+      </c>
+      <c r="K38" s="2">
+        <v>7</v>
+      </c>
+      <c r="L38" s="2">
+        <v>-1</v>
+      </c>
+      <c r="M38" s="2">
+        <v>-1</v>
+      </c>
+      <c r="N38" s="2">
+        <v>1</v>
+      </c>
+      <c r="O38" s="2">
+        <v>0</v>
+      </c>
+      <c r="P38" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="39" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C39" s="2">
-        <v>201</v>
+        <v>126</v>
       </c>
       <c r="D39" s="2">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>3852</v>
+        <v>3854</v>
       </c>
       <c r="F39" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G39" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H39" s="20" t="s">
-        <v>3853</v>
-      </c>
-      <c r="I39" s="20" t="s">
-        <v>3854</v>
+        <v>3848</v>
+      </c>
+      <c r="I39" s="22" t="s">
+        <v>3855</v>
       </c>
       <c r="J39" s="2">
         <v>-1</v>
       </c>
       <c r="K39" s="2">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="L39" s="2">
         <v>-1</v>
@@ -87148,103 +87237,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" s="2" customFormat="1" customHeight="1" spans="3:16">
-      <c r="C40" s="2">
-        <v>202</v>
-      </c>
-      <c r="D40" s="2">
-        <v>2</v>
-      </c>
-      <c r="E40" s="2" t="s">
-        <v>3855</v>
-      </c>
-      <c r="F40" s="2">
-        <v>12</v>
-      </c>
-      <c r="G40" s="2">
-        <v>12</v>
-      </c>
-      <c r="H40" s="20" t="s">
-        <v>3853</v>
-      </c>
-      <c r="I40" s="20" t="s">
-        <v>3856</v>
-      </c>
-      <c r="J40" s="2">
-        <v>-1</v>
-      </c>
-      <c r="K40" s="2">
-        <v>1</v>
-      </c>
-      <c r="L40" s="2">
-        <v>-1</v>
-      </c>
-      <c r="M40" s="2">
-        <v>-1</v>
-      </c>
-      <c r="N40" s="2">
-        <v>1</v>
-      </c>
-      <c r="O40" s="2">
-        <v>0</v>
-      </c>
-      <c r="P40" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" s="2" customFormat="1" customHeight="1" spans="3:16">
-      <c r="C41" s="2">
-        <v>203</v>
-      </c>
-      <c r="D41" s="2">
-        <v>3</v>
-      </c>
-      <c r="E41" s="2" t="s">
-        <v>3857</v>
-      </c>
-      <c r="F41" s="2">
-        <v>12</v>
-      </c>
-      <c r="G41" s="2">
-        <v>12</v>
-      </c>
-      <c r="H41" s="20" t="s">
-        <v>3853</v>
-      </c>
-      <c r="I41" s="22" t="s">
-        <v>3858</v>
-      </c>
-      <c r="J41" s="2">
-        <v>-1</v>
-      </c>
-      <c r="K41" s="2">
-        <v>1</v>
-      </c>
-      <c r="L41" s="2">
-        <v>-1</v>
-      </c>
-      <c r="M41" s="2">
-        <v>-1</v>
-      </c>
-      <c r="N41" s="2">
-        <v>1</v>
-      </c>
-      <c r="O41" s="2">
-        <v>0</v>
-      </c>
-      <c r="P41" s="2">
-        <v>0</v>
-      </c>
+    <row r="40" s="2" customFormat="1" customHeight="1" spans="9:9">
+      <c r="I40" s="9"/>
+    </row>
+    <row r="41" s="2" customFormat="1" customHeight="1" spans="9:9">
+      <c r="I41" s="9"/>
     </row>
     <row r="42" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C42" s="2">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="D42" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>3859</v>
+        <v>3856</v>
       </c>
       <c r="F42" s="2">
         <v>12</v>
@@ -87253,16 +87260,16 @@
         <v>12</v>
       </c>
       <c r="H42" s="20" t="s">
-        <v>3853</v>
-      </c>
-      <c r="I42" s="22" t="s">
-        <v>3860</v>
+        <v>3857</v>
+      </c>
+      <c r="I42" s="20" t="s">
+        <v>3858</v>
       </c>
       <c r="J42" s="2">
         <v>-1</v>
       </c>
       <c r="K42" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L42" s="2">
         <v>-1</v>
@@ -87282,13 +87289,13 @@
     </row>
     <row r="43" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C43" s="2">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="D43" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>3861</v>
+        <v>3859</v>
       </c>
       <c r="F43" s="2">
         <v>12</v>
@@ -87297,16 +87304,16 @@
         <v>12</v>
       </c>
       <c r="H43" s="20" t="s">
-        <v>3853</v>
-      </c>
-      <c r="I43" s="22" t="s">
-        <v>3794</v>
+        <v>3857</v>
+      </c>
+      <c r="I43" s="20" t="s">
+        <v>3860</v>
       </c>
       <c r="J43" s="2">
         <v>-1</v>
       </c>
       <c r="K43" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L43" s="2">
         <v>-1</v>
@@ -87326,13 +87333,13 @@
     </row>
     <row r="44" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C44" s="2">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="D44" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>3862</v>
+        <v>3861</v>
       </c>
       <c r="F44" s="2">
         <v>12</v>
@@ -87341,16 +87348,16 @@
         <v>12</v>
       </c>
       <c r="H44" s="20" t="s">
-        <v>3853</v>
+        <v>3857</v>
       </c>
       <c r="I44" s="22" t="s">
-        <v>3863</v>
+        <v>3862</v>
       </c>
       <c r="J44" s="2">
         <v>-1</v>
       </c>
       <c r="K44" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L44" s="2">
         <v>-1</v>
@@ -87370,13 +87377,13 @@
     </row>
     <row r="45" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C45" s="2">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="D45" s="2">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>3864</v>
+        <v>3863</v>
       </c>
       <c r="F45" s="2">
         <v>12</v>
@@ -87385,16 +87392,16 @@
         <v>12</v>
       </c>
       <c r="H45" s="20" t="s">
-        <v>3853</v>
+        <v>3857</v>
       </c>
       <c r="I45" s="22" t="s">
-        <v>3865</v>
+        <v>3864</v>
       </c>
       <c r="J45" s="2">
         <v>-1</v>
       </c>
       <c r="K45" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L45" s="2">
         <v>-1</v>
@@ -87414,13 +87421,13 @@
     </row>
     <row r="46" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C46" s="2">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="D46" s="2">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>3866</v>
+        <v>3865</v>
       </c>
       <c r="F46" s="2">
         <v>12</v>
@@ -87429,16 +87436,16 @@
         <v>12</v>
       </c>
       <c r="H46" s="20" t="s">
-        <v>3853</v>
+        <v>3857</v>
       </c>
       <c r="I46" s="22" t="s">
-        <v>3867</v>
+        <v>3794</v>
       </c>
       <c r="J46" s="2">
         <v>-1</v>
       </c>
       <c r="K46" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L46" s="2">
         <v>-1</v>
@@ -87458,13 +87465,13 @@
     </row>
     <row r="47" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C47" s="2">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="D47" s="2">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>3868</v>
+        <v>3866</v>
       </c>
       <c r="F47" s="2">
         <v>12</v>
@@ -87473,16 +87480,16 @@
         <v>12</v>
       </c>
       <c r="H47" s="20" t="s">
-        <v>3853</v>
+        <v>3857</v>
       </c>
       <c r="I47" s="22" t="s">
-        <v>3869</v>
+        <v>3867</v>
       </c>
       <c r="J47" s="2">
         <v>-1</v>
       </c>
       <c r="K47" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L47" s="2">
         <v>-1</v>
@@ -87502,13 +87509,13 @@
     </row>
     <row r="48" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C48" s="2">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="D48" s="2">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>3870</v>
+        <v>3868</v>
       </c>
       <c r="F48" s="2">
         <v>12</v>
@@ -87517,16 +87524,16 @@
         <v>12</v>
       </c>
       <c r="H48" s="20" t="s">
-        <v>3853</v>
+        <v>3857</v>
       </c>
       <c r="I48" s="22" t="s">
-        <v>3791</v>
+        <v>3869</v>
       </c>
       <c r="J48" s="2">
         <v>-1</v>
       </c>
       <c r="K48" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L48" s="2">
         <v>-1</v>
@@ -87546,13 +87553,13 @@
     </row>
     <row r="49" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C49" s="2">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="D49" s="2">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>3871</v>
+        <v>3870</v>
       </c>
       <c r="F49" s="2">
         <v>12</v>
@@ -87561,16 +87568,16 @@
         <v>12</v>
       </c>
       <c r="H49" s="20" t="s">
-        <v>3853</v>
+        <v>3857</v>
       </c>
       <c r="I49" s="22" t="s">
-        <v>3872</v>
+        <v>3871</v>
       </c>
       <c r="J49" s="2">
         <v>-1</v>
       </c>
       <c r="K49" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L49" s="2">
         <v>-1</v>
@@ -87590,13 +87597,13 @@
     </row>
     <row r="50" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C50" s="2">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="D50" s="2">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>3873</v>
+        <v>3872</v>
       </c>
       <c r="F50" s="2">
         <v>12</v>
@@ -87605,16 +87612,16 @@
         <v>12</v>
       </c>
       <c r="H50" s="20" t="s">
-        <v>3853</v>
+        <v>3857</v>
       </c>
       <c r="I50" s="22" t="s">
-        <v>3874</v>
+        <v>3873</v>
       </c>
       <c r="J50" s="2">
         <v>-1</v>
       </c>
       <c r="K50" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L50" s="2">
         <v>-1</v>
@@ -87634,13 +87641,13 @@
     </row>
     <row r="51" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C51" s="2">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="D51" s="2">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>3875</v>
+        <v>3874</v>
       </c>
       <c r="F51" s="2">
         <v>12</v>
@@ -87649,16 +87656,16 @@
         <v>12</v>
       </c>
       <c r="H51" s="20" t="s">
-        <v>3853</v>
+        <v>3857</v>
       </c>
       <c r="I51" s="22" t="s">
-        <v>3876</v>
+        <v>3791</v>
       </c>
       <c r="J51" s="2">
         <v>-1</v>
       </c>
       <c r="K51" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L51" s="2">
         <v>-1</v>
@@ -87678,13 +87685,13 @@
     </row>
     <row r="52" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C52" s="2">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="D52" s="2">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>3877</v>
+        <v>3875</v>
       </c>
       <c r="F52" s="2">
         <v>12</v>
@@ -87693,16 +87700,16 @@
         <v>12</v>
       </c>
       <c r="H52" s="20" t="s">
-        <v>3853</v>
+        <v>3857</v>
       </c>
       <c r="I52" s="22" t="s">
-        <v>3878</v>
+        <v>3876</v>
       </c>
       <c r="J52" s="2">
         <v>-1</v>
       </c>
       <c r="K52" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L52" s="2">
         <v>-1</v>
@@ -87722,13 +87729,13 @@
     </row>
     <row r="53" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C53" s="2">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="D53" s="2">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>3879</v>
+        <v>3877</v>
       </c>
       <c r="F53" s="2">
         <v>12</v>
@@ -87737,16 +87744,16 @@
         <v>12</v>
       </c>
       <c r="H53" s="20" t="s">
-        <v>3853</v>
+        <v>3857</v>
       </c>
       <c r="I53" s="22" t="s">
-        <v>3880</v>
+        <v>3878</v>
       </c>
       <c r="J53" s="2">
         <v>-1</v>
       </c>
       <c r="K53" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L53" s="2">
         <v>-1</v>
@@ -87766,13 +87773,13 @@
     </row>
     <row r="54" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C54" s="2">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="D54" s="2">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>3881</v>
+        <v>3879</v>
       </c>
       <c r="F54" s="2">
         <v>12</v>
@@ -87781,10 +87788,10 @@
         <v>12</v>
       </c>
       <c r="H54" s="20" t="s">
-        <v>3853</v>
+        <v>3857</v>
       </c>
       <c r="I54" s="22" t="s">
-        <v>3882</v>
+        <v>3880</v>
       </c>
       <c r="J54" s="2">
         <v>-1</v>
@@ -87810,13 +87817,13 @@
     </row>
     <row r="55" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C55" s="2">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="D55" s="2">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>3883</v>
+        <v>3881</v>
       </c>
       <c r="F55" s="2">
         <v>12</v>
@@ -87825,10 +87832,10 @@
         <v>12</v>
       </c>
       <c r="H55" s="20" t="s">
-        <v>3853</v>
+        <v>3857</v>
       </c>
       <c r="I55" s="22" t="s">
-        <v>3884</v>
+        <v>3882</v>
       </c>
       <c r="J55" s="2">
         <v>-1</v>
@@ -87854,13 +87861,13 @@
     </row>
     <row r="56" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C56" s="2">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="D56" s="2">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>3885</v>
+        <v>3883</v>
       </c>
       <c r="F56" s="2">
         <v>12</v>
@@ -87869,10 +87876,10 @@
         <v>12</v>
       </c>
       <c r="H56" s="20" t="s">
-        <v>3853</v>
+        <v>3857</v>
       </c>
       <c r="I56" s="22" t="s">
-        <v>3886</v>
+        <v>3884</v>
       </c>
       <c r="J56" s="2">
         <v>-1</v>
@@ -87898,13 +87905,13 @@
     </row>
     <row r="57" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C57" s="2">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="D57" s="2">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>3887</v>
+        <v>3885</v>
       </c>
       <c r="F57" s="2">
         <v>12</v>
@@ -87913,10 +87920,10 @@
         <v>12</v>
       </c>
       <c r="H57" s="20" t="s">
-        <v>3853</v>
+        <v>3857</v>
       </c>
       <c r="I57" s="22" t="s">
-        <v>3888</v>
+        <v>3886</v>
       </c>
       <c r="J57" s="2">
         <v>-1</v>
@@ -87942,13 +87949,13 @@
     </row>
     <row r="58" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C58" s="2">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="D58" s="2">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>3889</v>
+        <v>3887</v>
       </c>
       <c r="F58" s="2">
         <v>12</v>
@@ -87957,16 +87964,16 @@
         <v>12</v>
       </c>
       <c r="H58" s="20" t="s">
-        <v>3890</v>
+        <v>3857</v>
       </c>
       <c r="I58" s="22" t="s">
-        <v>3891</v>
+        <v>3888</v>
       </c>
       <c r="J58" s="2">
         <v>-1</v>
       </c>
       <c r="K58" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L58" s="2">
         <v>-1</v>
@@ -87986,13 +87993,13 @@
     </row>
     <row r="59" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C59" s="2">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="D59" s="2">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>3892</v>
+        <v>3889</v>
       </c>
       <c r="F59" s="2">
         <v>12</v>
@@ -88001,16 +88008,16 @@
         <v>12</v>
       </c>
       <c r="H59" s="20" t="s">
+        <v>3857</v>
+      </c>
+      <c r="I59" s="22" t="s">
         <v>3890</v>
-      </c>
-      <c r="I59" s="22" t="s">
-        <v>3893</v>
       </c>
       <c r="J59" s="2">
         <v>-1</v>
       </c>
       <c r="K59" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L59" s="2">
         <v>-1</v>
@@ -88030,13 +88037,13 @@
     </row>
     <row r="60" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C60" s="2">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="D60" s="2">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>3894</v>
+        <v>3891</v>
       </c>
       <c r="F60" s="2">
         <v>12</v>
@@ -88045,16 +88052,16 @@
         <v>12</v>
       </c>
       <c r="H60" s="20" t="s">
-        <v>3895</v>
+        <v>3857</v>
       </c>
       <c r="I60" s="22" t="s">
-        <v>3896</v>
+        <v>3892</v>
       </c>
       <c r="J60" s="2">
         <v>-1</v>
       </c>
       <c r="K60" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L60" s="2">
         <v>-1</v>
@@ -88074,13 +88081,13 @@
     </row>
     <row r="61" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C61" s="2">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="D61" s="2">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>3897</v>
+        <v>3893</v>
       </c>
       <c r="F61" s="2">
         <v>12</v>
@@ -88089,16 +88096,16 @@
         <v>12</v>
       </c>
       <c r="H61" s="20" t="s">
-        <v>3898</v>
+        <v>3894</v>
       </c>
       <c r="I61" s="22" t="s">
-        <v>3899</v>
+        <v>3895</v>
       </c>
       <c r="J61" s="2">
         <v>-1</v>
       </c>
       <c r="K61" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L61" s="2">
         <v>-1</v>
@@ -88118,13 +88125,13 @@
     </row>
     <row r="62" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C62" s="2">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="D62" s="2">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>3900</v>
+        <v>3896</v>
       </c>
       <c r="F62" s="2">
         <v>12</v>
@@ -88133,16 +88140,16 @@
         <v>12</v>
       </c>
       <c r="H62" s="20" t="s">
-        <v>3898</v>
+        <v>3894</v>
       </c>
       <c r="I62" s="22" t="s">
-        <v>3901</v>
+        <v>3897</v>
       </c>
       <c r="J62" s="2">
         <v>-1</v>
       </c>
       <c r="K62" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L62" s="2">
         <v>-1</v>
@@ -88160,39 +88167,121 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" s="2" customFormat="1" customHeight="1" spans="9:9">
-      <c r="I63" s="9"/>
-    </row>
-    <row r="64" s="2" customFormat="1" customHeight="1" spans="9:9">
-      <c r="I64" s="9"/>
+    <row r="63" s="2" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C63" s="2">
+        <v>222</v>
+      </c>
+      <c r="D63" s="2">
+        <v>22</v>
+      </c>
+      <c r="E63" s="2" t="s">
+        <v>3898</v>
+      </c>
+      <c r="F63" s="2">
+        <v>12</v>
+      </c>
+      <c r="G63" s="2">
+        <v>12</v>
+      </c>
+      <c r="H63" s="20" t="s">
+        <v>3899</v>
+      </c>
+      <c r="I63" s="22" t="s">
+        <v>3900</v>
+      </c>
+      <c r="J63" s="2">
+        <v>-1</v>
+      </c>
+      <c r="K63" s="2">
+        <v>6</v>
+      </c>
+      <c r="L63" s="2">
+        <v>-1</v>
+      </c>
+      <c r="M63" s="2">
+        <v>-1</v>
+      </c>
+      <c r="N63" s="2">
+        <v>1</v>
+      </c>
+      <c r="O63" s="2">
+        <v>0</v>
+      </c>
+      <c r="P63" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" s="2" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C64" s="2">
+        <v>223</v>
+      </c>
+      <c r="D64" s="2">
+        <v>23</v>
+      </c>
+      <c r="E64" s="2" t="s">
+        <v>3901</v>
+      </c>
+      <c r="F64" s="2">
+        <v>12</v>
+      </c>
+      <c r="G64" s="2">
+        <v>12</v>
+      </c>
+      <c r="H64" s="20" t="s">
+        <v>3902</v>
+      </c>
+      <c r="I64" s="22" t="s">
+        <v>3903</v>
+      </c>
+      <c r="J64" s="2">
+        <v>-1</v>
+      </c>
+      <c r="K64" s="2">
+        <v>7</v>
+      </c>
+      <c r="L64" s="2">
+        <v>-1</v>
+      </c>
+      <c r="M64" s="2">
+        <v>-1</v>
+      </c>
+      <c r="N64" s="2">
+        <v>1</v>
+      </c>
+      <c r="O64" s="2">
+        <v>0</v>
+      </c>
+      <c r="P64" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="65" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C65" s="2">
-        <v>301</v>
+        <v>224</v>
       </c>
       <c r="D65" s="2">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="E65" s="2" t="s">
+        <v>3904</v>
+      </c>
+      <c r="F65" s="2">
+        <v>12</v>
+      </c>
+      <c r="G65" s="2">
+        <v>12</v>
+      </c>
+      <c r="H65" s="20" t="s">
         <v>3902</v>
       </c>
-      <c r="F65" s="2">
-        <v>13</v>
-      </c>
-      <c r="G65" s="2">
-        <v>13</v>
-      </c>
-      <c r="H65" s="20" t="s">
-        <v>3903</v>
-      </c>
       <c r="I65" s="22" t="s">
-        <v>3904</v>
+        <v>3905</v>
       </c>
       <c r="J65" s="2">
         <v>-1</v>
       </c>
       <c r="K65" s="2">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="L65" s="2">
         <v>-1</v>
@@ -88212,31 +88301,31 @@
     </row>
     <row r="66" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C66" s="2">
-        <v>302</v>
+        <v>225</v>
       </c>
       <c r="D66" s="2">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>3905</v>
+        <v>3906</v>
       </c>
       <c r="F66" s="2">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G66" s="2">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H66" s="20" t="s">
-        <v>3903</v>
+        <v>3902</v>
       </c>
       <c r="I66" s="22" t="s">
-        <v>3906</v>
+        <v>3907</v>
       </c>
       <c r="J66" s="2">
         <v>-1</v>
       </c>
       <c r="K66" s="2">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="L66" s="2">
         <v>-1</v>
@@ -88256,31 +88345,31 @@
     </row>
     <row r="67" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C67" s="2">
-        <v>303</v>
+        <v>226</v>
       </c>
       <c r="D67" s="2">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>3907</v>
+        <v>3908</v>
       </c>
       <c r="F67" s="2">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G67" s="2">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H67" s="20" t="s">
-        <v>3903</v>
+        <v>3902</v>
       </c>
       <c r="I67" s="22" t="s">
-        <v>3908</v>
+        <v>3909</v>
       </c>
       <c r="J67" s="2">
         <v>-1</v>
       </c>
       <c r="K67" s="2">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="L67" s="2">
         <v>-1</v>
@@ -88298,59 +88387,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" s="2" customFormat="1" customHeight="1" spans="3:16">
-      <c r="C68" s="2">
-        <v>304</v>
-      </c>
-      <c r="D68" s="2">
-        <v>4</v>
-      </c>
-      <c r="E68" s="2" t="s">
-        <v>3909</v>
-      </c>
-      <c r="F68" s="2">
-        <v>13</v>
-      </c>
-      <c r="G68" s="2">
-        <v>13</v>
-      </c>
-      <c r="H68" s="20" t="s">
-        <v>3903</v>
-      </c>
-      <c r="I68" s="22" t="s">
-        <v>3910</v>
-      </c>
-      <c r="J68" s="2">
-        <v>-1</v>
-      </c>
-      <c r="K68" s="2">
-        <v>2</v>
-      </c>
-      <c r="L68" s="2">
-        <v>-1</v>
-      </c>
-      <c r="M68" s="2">
-        <v>-1</v>
-      </c>
-      <c r="N68" s="2">
-        <v>1</v>
-      </c>
-      <c r="O68" s="2">
-        <v>0</v>
-      </c>
-      <c r="P68" s="2">
-        <v>0</v>
-      </c>
+    <row r="68" s="2" customFormat="1" customHeight="1" spans="9:9">
+      <c r="I68" s="9"/>
     </row>
     <row r="69" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C69" s="2">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="D69" s="2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>3911</v>
+        <v>3910</v>
       </c>
       <c r="F69" s="2">
         <v>13</v>
@@ -88359,7 +88407,7 @@
         <v>13</v>
       </c>
       <c r="H69" s="20" t="s">
-        <v>3903</v>
+        <v>3911</v>
       </c>
       <c r="I69" s="22" t="s">
         <v>3912</v>
@@ -88368,7 +88416,7 @@
         <v>-1</v>
       </c>
       <c r="K69" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L69" s="2">
         <v>-1</v>
@@ -88388,10 +88436,10 @@
     </row>
     <row r="70" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C70" s="2">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="D70" s="2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E70" s="2" t="s">
         <v>3913</v>
@@ -88403,7 +88451,7 @@
         <v>13</v>
       </c>
       <c r="H70" s="20" t="s">
-        <v>3903</v>
+        <v>3911</v>
       </c>
       <c r="I70" s="22" t="s">
         <v>3914</v>
@@ -88412,7 +88460,7 @@
         <v>-1</v>
       </c>
       <c r="K70" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L70" s="2">
         <v>-1</v>
@@ -88432,10 +88480,10 @@
     </row>
     <row r="71" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C71" s="2">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="D71" s="2">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E71" s="2" t="s">
         <v>3915</v>
@@ -88447,7 +88495,7 @@
         <v>13</v>
       </c>
       <c r="H71" s="20" t="s">
-        <v>3903</v>
+        <v>3911</v>
       </c>
       <c r="I71" s="22" t="s">
         <v>3916</v>
@@ -88456,7 +88504,7 @@
         <v>-1</v>
       </c>
       <c r="K71" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L71" s="2">
         <v>-1</v>
@@ -88476,10 +88524,10 @@
     </row>
     <row r="72" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C72" s="2">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="D72" s="2">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E72" s="2" t="s">
         <v>3917</v>
@@ -88491,7 +88539,7 @@
         <v>13</v>
       </c>
       <c r="H72" s="20" t="s">
-        <v>3903</v>
+        <v>3911</v>
       </c>
       <c r="I72" s="22" t="s">
         <v>3918</v>
@@ -88500,7 +88548,7 @@
         <v>-1</v>
       </c>
       <c r="K72" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L72" s="2">
         <v>-1</v>
@@ -88520,10 +88568,10 @@
     </row>
     <row r="73" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C73" s="2">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="D73" s="2">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E73" s="2" t="s">
         <v>3919</v>
@@ -88535,7 +88583,7 @@
         <v>13</v>
       </c>
       <c r="H73" s="20" t="s">
-        <v>3903</v>
+        <v>3911</v>
       </c>
       <c r="I73" s="22" t="s">
         <v>3920</v>
@@ -88544,7 +88592,7 @@
         <v>-1</v>
       </c>
       <c r="K73" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L73" s="2">
         <v>-1</v>
@@ -88564,10 +88612,10 @@
     </row>
     <row r="74" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C74" s="2">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="D74" s="2">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E74" s="2" t="s">
         <v>3921</v>
@@ -88579,7 +88627,7 @@
         <v>13</v>
       </c>
       <c r="H74" s="20" t="s">
-        <v>3903</v>
+        <v>3911</v>
       </c>
       <c r="I74" s="22" t="s">
         <v>3922</v>
@@ -88588,7 +88636,7 @@
         <v>-1</v>
       </c>
       <c r="K74" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L74" s="2">
         <v>-1</v>
@@ -88608,10 +88656,10 @@
     </row>
     <row r="75" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C75" s="2">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="D75" s="2">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E75" s="2" t="s">
         <v>3923</v>
@@ -88623,7 +88671,7 @@
         <v>13</v>
       </c>
       <c r="H75" s="20" t="s">
-        <v>3903</v>
+        <v>3911</v>
       </c>
       <c r="I75" s="22" t="s">
         <v>3924</v>
@@ -88632,7 +88680,7 @@
         <v>-1</v>
       </c>
       <c r="K75" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L75" s="2">
         <v>-1</v>
@@ -88652,10 +88700,10 @@
     </row>
     <row r="76" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C76" s="2">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="D76" s="2">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E76" s="2" t="s">
         <v>3925</v>
@@ -88667,7 +88715,7 @@
         <v>13</v>
       </c>
       <c r="H76" s="20" t="s">
-        <v>3903</v>
+        <v>3911</v>
       </c>
       <c r="I76" s="22" t="s">
         <v>3926</v>
@@ -88676,7 +88724,7 @@
         <v>-1</v>
       </c>
       <c r="K76" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L76" s="2">
         <v>-1</v>
@@ -88696,10 +88744,10 @@
     </row>
     <row r="77" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C77" s="2">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="D77" s="2">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E77" s="2" t="s">
         <v>3927</v>
@@ -88711,7 +88759,7 @@
         <v>13</v>
       </c>
       <c r="H77" s="20" t="s">
-        <v>3903</v>
+        <v>3911</v>
       </c>
       <c r="I77" s="22" t="s">
         <v>3928</v>
@@ -88720,7 +88768,7 @@
         <v>-1</v>
       </c>
       <c r="K77" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L77" s="2">
         <v>-1</v>
@@ -88740,10 +88788,10 @@
     </row>
     <row r="78" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C78" s="2">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="D78" s="2">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E78" s="2" t="s">
         <v>3929</v>
@@ -88755,7 +88803,7 @@
         <v>13</v>
       </c>
       <c r="H78" s="20" t="s">
-        <v>3903</v>
+        <v>3911</v>
       </c>
       <c r="I78" s="22" t="s">
         <v>3930</v>
@@ -88764,7 +88812,7 @@
         <v>-1</v>
       </c>
       <c r="K78" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L78" s="2">
         <v>-1</v>
@@ -88784,10 +88832,10 @@
     </row>
     <row r="79" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C79" s="2">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="D79" s="2">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E79" s="2" t="s">
         <v>3931</v>
@@ -88799,7 +88847,7 @@
         <v>13</v>
       </c>
       <c r="H79" s="20" t="s">
-        <v>3903</v>
+        <v>3911</v>
       </c>
       <c r="I79" s="22" t="s">
         <v>3932</v>
@@ -88808,7 +88856,7 @@
         <v>-1</v>
       </c>
       <c r="K79" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L79" s="2">
         <v>-1</v>
@@ -88828,10 +88876,10 @@
     </row>
     <row r="80" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C80" s="2">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="D80" s="2">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E80" s="2" t="s">
         <v>3933</v>
@@ -88843,7 +88891,7 @@
         <v>13</v>
       </c>
       <c r="H80" s="20" t="s">
-        <v>3903</v>
+        <v>3911</v>
       </c>
       <c r="I80" s="22" t="s">
         <v>3934</v>
@@ -88852,7 +88900,7 @@
         <v>-1</v>
       </c>
       <c r="K80" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L80" s="2">
         <v>-1</v>
@@ -88872,10 +88920,10 @@
     </row>
     <row r="81" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C81" s="2">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="D81" s="2">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E81" s="2" t="s">
         <v>3935</v>
@@ -88887,7 +88935,7 @@
         <v>13</v>
       </c>
       <c r="H81" s="20" t="s">
-        <v>3903</v>
+        <v>3911</v>
       </c>
       <c r="I81" s="22" t="s">
         <v>3936</v>
@@ -88916,10 +88964,10 @@
     </row>
     <row r="82" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C82" s="2">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="D82" s="2">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E82" s="2" t="s">
         <v>3937</v>
@@ -88931,7 +88979,7 @@
         <v>13</v>
       </c>
       <c r="H82" s="20" t="s">
-        <v>3903</v>
+        <v>3911</v>
       </c>
       <c r="I82" s="22" t="s">
         <v>3938</v>
@@ -88960,10 +89008,10 @@
     </row>
     <row r="83" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C83" s="2">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="D83" s="2">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E83" s="2" t="s">
         <v>3939</v>
@@ -88975,7 +89023,7 @@
         <v>13</v>
       </c>
       <c r="H83" s="20" t="s">
-        <v>3903</v>
+        <v>3911</v>
       </c>
       <c r="I83" s="22" t="s">
         <v>3940</v>
@@ -89004,10 +89052,10 @@
     </row>
     <row r="84" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C84" s="2">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="D84" s="2">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E84" s="2" t="s">
         <v>3941</v>
@@ -89019,16 +89067,16 @@
         <v>13</v>
       </c>
       <c r="H84" s="20" t="s">
+        <v>3911</v>
+      </c>
+      <c r="I84" s="22" t="s">
         <v>3942</v>
-      </c>
-      <c r="I84" s="22" t="s">
-        <v>3943</v>
       </c>
       <c r="J84" s="2">
         <v>-1</v>
       </c>
       <c r="K84" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L84" s="2">
         <v>-1</v>
@@ -89048,13 +89096,13 @@
     </row>
     <row r="85" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C85" s="2">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="D85" s="2">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>3944</v>
+        <v>3943</v>
       </c>
       <c r="F85" s="2">
         <v>13</v>
@@ -89063,16 +89111,16 @@
         <v>13</v>
       </c>
       <c r="H85" s="20" t="s">
-        <v>3942</v>
+        <v>3911</v>
       </c>
       <c r="I85" s="22" t="s">
-        <v>3945</v>
+        <v>3944</v>
       </c>
       <c r="J85" s="2">
         <v>-1</v>
       </c>
       <c r="K85" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L85" s="2">
         <v>-1</v>
@@ -89092,13 +89140,13 @@
     </row>
     <row r="86" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C86" s="2">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="D86" s="2">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>3946</v>
+        <v>3945</v>
       </c>
       <c r="F86" s="2">
         <v>13</v>
@@ -89107,16 +89155,16 @@
         <v>13</v>
       </c>
       <c r="H86" s="20" t="s">
-        <v>3942</v>
+        <v>3911</v>
       </c>
       <c r="I86" s="22" t="s">
-        <v>3947</v>
+        <v>3946</v>
       </c>
       <c r="J86" s="2">
         <v>-1</v>
       </c>
       <c r="K86" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L86" s="2">
         <v>-1</v>
@@ -89136,13 +89184,13 @@
     </row>
     <row r="87" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C87" s="2">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="D87" s="2">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>3948</v>
+        <v>3947</v>
       </c>
       <c r="F87" s="2">
         <v>13</v>
@@ -89151,16 +89199,16 @@
         <v>13</v>
       </c>
       <c r="H87" s="20" t="s">
-        <v>3942</v>
+        <v>3911</v>
       </c>
       <c r="I87" s="22" t="s">
-        <v>3949</v>
+        <v>3948</v>
       </c>
       <c r="J87" s="2">
         <v>-1</v>
       </c>
       <c r="K87" s="2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L87" s="2">
         <v>-1</v>
@@ -89180,13 +89228,13 @@
     </row>
     <row r="88" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C88" s="2">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="D88" s="2">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>3950</v>
+        <v>3949</v>
       </c>
       <c r="F88" s="2">
         <v>13</v>
@@ -89195,7 +89243,7 @@
         <v>13</v>
       </c>
       <c r="H88" s="20" t="s">
-        <v>3942</v>
+        <v>3950</v>
       </c>
       <c r="I88" s="22" t="s">
         <v>3951</v>
@@ -89204,7 +89252,7 @@
         <v>-1</v>
       </c>
       <c r="K88" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L88" s="2">
         <v>-1</v>
@@ -89222,39 +89270,121 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" s="2" customFormat="1" customHeight="1" spans="9:9">
-      <c r="I89" s="9"/>
-    </row>
-    <row r="90" s="2" customFormat="1" customHeight="1" spans="9:9">
-      <c r="I90" s="9"/>
+    <row r="89" s="2" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C89" s="2">
+        <v>321</v>
+      </c>
+      <c r="D89" s="2">
+        <v>21</v>
+      </c>
+      <c r="E89" s="2" t="s">
+        <v>3952</v>
+      </c>
+      <c r="F89" s="2">
+        <v>13</v>
+      </c>
+      <c r="G89" s="2">
+        <v>13</v>
+      </c>
+      <c r="H89" s="20" t="s">
+        <v>3950</v>
+      </c>
+      <c r="I89" s="22" t="s">
+        <v>3953</v>
+      </c>
+      <c r="J89" s="2">
+        <v>-1</v>
+      </c>
+      <c r="K89" s="2">
+        <v>6</v>
+      </c>
+      <c r="L89" s="2">
+        <v>-1</v>
+      </c>
+      <c r="M89" s="2">
+        <v>-1</v>
+      </c>
+      <c r="N89" s="2">
+        <v>1</v>
+      </c>
+      <c r="O89" s="2">
+        <v>0</v>
+      </c>
+      <c r="P89" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" s="2" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C90" s="2">
+        <v>322</v>
+      </c>
+      <c r="D90" s="2">
+        <v>22</v>
+      </c>
+      <c r="E90" s="2" t="s">
+        <v>3954</v>
+      </c>
+      <c r="F90" s="2">
+        <v>13</v>
+      </c>
+      <c r="G90" s="2">
+        <v>13</v>
+      </c>
+      <c r="H90" s="20" t="s">
+        <v>3950</v>
+      </c>
+      <c r="I90" s="22" t="s">
+        <v>3955</v>
+      </c>
+      <c r="J90" s="2">
+        <v>-1</v>
+      </c>
+      <c r="K90" s="2">
+        <v>6</v>
+      </c>
+      <c r="L90" s="2">
+        <v>-1</v>
+      </c>
+      <c r="M90" s="2">
+        <v>-1</v>
+      </c>
+      <c r="N90" s="2">
+        <v>1</v>
+      </c>
+      <c r="O90" s="2">
+        <v>0</v>
+      </c>
+      <c r="P90" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="91" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C91" s="2">
-        <v>401</v>
+        <v>323</v>
       </c>
       <c r="D91" s="2">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>3952</v>
+        <v>3956</v>
       </c>
       <c r="F91" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G91" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H91" s="20" t="s">
-        <v>3953</v>
-      </c>
-      <c r="I91" s="20" t="s">
-        <v>3954</v>
+        <v>3950</v>
+      </c>
+      <c r="I91" s="22" t="s">
+        <v>3957</v>
       </c>
       <c r="J91" s="2">
         <v>-1</v>
       </c>
       <c r="K91" s="2">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="L91" s="2">
         <v>-1</v>
@@ -89274,31 +89404,31 @@
     </row>
     <row r="92" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C92" s="2">
-        <v>402</v>
+        <v>324</v>
       </c>
       <c r="D92" s="2">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>3955</v>
+        <v>3958</v>
       </c>
       <c r="F92" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G92" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H92" s="20" t="s">
-        <v>3953</v>
-      </c>
-      <c r="I92" s="20" t="s">
-        <v>3956</v>
+        <v>3950</v>
+      </c>
+      <c r="I92" s="22" t="s">
+        <v>3959</v>
       </c>
       <c r="J92" s="2">
         <v>-1</v>
       </c>
       <c r="K92" s="2">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="L92" s="2">
         <v>-1</v>
@@ -89318,31 +89448,31 @@
     </row>
     <row r="93" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C93" s="2">
-        <v>403</v>
+        <v>325</v>
       </c>
       <c r="D93" s="2">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>3957</v>
+        <v>3960</v>
       </c>
       <c r="F93" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G93" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H93" s="20" t="s">
-        <v>3953</v>
-      </c>
-      <c r="I93" s="20" t="s">
-        <v>3958</v>
+        <v>3950</v>
+      </c>
+      <c r="I93" s="22" t="s">
+        <v>3961</v>
       </c>
       <c r="J93" s="2">
         <v>-1</v>
       </c>
       <c r="K93" s="2">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="L93" s="2">
         <v>-1</v>
@@ -89362,31 +89492,31 @@
     </row>
     <row r="94" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C94" s="2">
-        <v>404</v>
+        <v>326</v>
       </c>
       <c r="D94" s="2">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>3959</v>
+        <v>3962</v>
       </c>
       <c r="F94" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G94" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H94" s="20" t="s">
-        <v>3953</v>
-      </c>
-      <c r="I94" s="20" t="s">
-        <v>3960</v>
+        <v>3950</v>
+      </c>
+      <c r="I94" s="22" t="s">
+        <v>3963</v>
       </c>
       <c r="J94" s="2">
         <v>-1</v>
       </c>
       <c r="K94" s="2">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="L94" s="2">
         <v>-1</v>
@@ -89404,103 +89534,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" s="2" customFormat="1" customHeight="1" spans="3:16">
-      <c r="C95" s="2">
-        <v>405</v>
-      </c>
-      <c r="D95" s="2">
-        <v>5</v>
-      </c>
-      <c r="E95" s="2" t="s">
-        <v>3961</v>
-      </c>
-      <c r="F95" s="2">
-        <v>14</v>
-      </c>
-      <c r="G95" s="2">
-        <v>14</v>
-      </c>
-      <c r="H95" s="20" t="s">
-        <v>3953</v>
-      </c>
-      <c r="I95" s="20" t="s">
-        <v>3962</v>
-      </c>
-      <c r="J95" s="2">
-        <v>-1</v>
-      </c>
-      <c r="K95" s="2">
-        <v>2</v>
-      </c>
-      <c r="L95" s="2">
-        <v>-1</v>
-      </c>
-      <c r="M95" s="2">
-        <v>-1</v>
-      </c>
-      <c r="N95" s="2">
-        <v>1</v>
-      </c>
-      <c r="O95" s="2">
-        <v>0</v>
-      </c>
-      <c r="P95" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="96" s="2" customFormat="1" customHeight="1" spans="3:16">
-      <c r="C96" s="2">
-        <v>406</v>
-      </c>
-      <c r="D96" s="2">
-        <v>6</v>
-      </c>
-      <c r="E96" s="2" t="s">
-        <v>3963</v>
-      </c>
-      <c r="F96" s="2">
-        <v>14</v>
-      </c>
-      <c r="G96" s="2">
-        <v>14</v>
-      </c>
-      <c r="H96" s="20" t="s">
-        <v>3953</v>
-      </c>
-      <c r="I96" s="20" t="s">
-        <v>3964</v>
-      </c>
-      <c r="J96" s="2">
-        <v>-1</v>
-      </c>
-      <c r="K96" s="2">
-        <v>2</v>
-      </c>
-      <c r="L96" s="2">
-        <v>-1</v>
-      </c>
-      <c r="M96" s="2">
-        <v>-1</v>
-      </c>
-      <c r="N96" s="2">
-        <v>1</v>
-      </c>
-      <c r="O96" s="2">
-        <v>0</v>
-      </c>
-      <c r="P96" s="2">
-        <v>0</v>
-      </c>
+    <row r="95" s="2" customFormat="1" customHeight="1" spans="9:9">
+      <c r="I95" s="9"/>
+    </row>
+    <row r="96" s="2" customFormat="1" customHeight="1" spans="9:9">
+      <c r="I96" s="9"/>
     </row>
     <row r="97" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C97" s="2">
-        <v>407</v>
+        <v>401</v>
       </c>
       <c r="D97" s="2">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>3965</v>
+        <v>3964</v>
       </c>
       <c r="F97" s="2">
         <v>14</v>
@@ -89509,7 +89557,7 @@
         <v>14</v>
       </c>
       <c r="H97" s="20" t="s">
-        <v>3953</v>
+        <v>3965</v>
       </c>
       <c r="I97" s="20" t="s">
         <v>3966</v>
@@ -89518,7 +89566,7 @@
         <v>-1</v>
       </c>
       <c r="K97" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L97" s="2">
         <v>-1</v>
@@ -89538,10 +89586,10 @@
     </row>
     <row r="98" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C98" s="2">
-        <v>408</v>
+        <v>402</v>
       </c>
       <c r="D98" s="2">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E98" s="2" t="s">
         <v>3967</v>
@@ -89553,7 +89601,7 @@
         <v>14</v>
       </c>
       <c r="H98" s="20" t="s">
-        <v>3953</v>
+        <v>3965</v>
       </c>
       <c r="I98" s="20" t="s">
         <v>3968</v>
@@ -89562,7 +89610,7 @@
         <v>-1</v>
       </c>
       <c r="K98" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L98" s="2">
         <v>-1</v>
@@ -89582,10 +89630,10 @@
     </row>
     <row r="99" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C99" s="2">
-        <v>409</v>
+        <v>403</v>
       </c>
       <c r="D99" s="2">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E99" s="2" t="s">
         <v>3969</v>
@@ -89597,7 +89645,7 @@
         <v>14</v>
       </c>
       <c r="H99" s="20" t="s">
-        <v>3953</v>
+        <v>3965</v>
       </c>
       <c r="I99" s="20" t="s">
         <v>3970</v>
@@ -89606,7 +89654,7 @@
         <v>-1</v>
       </c>
       <c r="K99" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L99" s="2">
         <v>-1</v>
@@ -89626,10 +89674,10 @@
     </row>
     <row r="100" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C100" s="2">
-        <v>410</v>
+        <v>404</v>
       </c>
       <c r="D100" s="2">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E100" s="2" t="s">
         <v>3971</v>
@@ -89641,7 +89689,7 @@
         <v>14</v>
       </c>
       <c r="H100" s="20" t="s">
-        <v>3953</v>
+        <v>3965</v>
       </c>
       <c r="I100" s="20" t="s">
         <v>3972</v>
@@ -89650,7 +89698,7 @@
         <v>-1</v>
       </c>
       <c r="K100" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L100" s="2">
         <v>-1</v>
@@ -89670,10 +89718,10 @@
     </row>
     <row r="101" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C101" s="2">
-        <v>411</v>
+        <v>405</v>
       </c>
       <c r="D101" s="2">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E101" s="2" t="s">
         <v>3973</v>
@@ -89685,7 +89733,7 @@
         <v>14</v>
       </c>
       <c r="H101" s="20" t="s">
-        <v>3953</v>
+        <v>3965</v>
       </c>
       <c r="I101" s="20" t="s">
         <v>3974</v>
@@ -89694,7 +89742,7 @@
         <v>-1</v>
       </c>
       <c r="K101" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L101" s="2">
         <v>-1</v>
@@ -89714,10 +89762,10 @@
     </row>
     <row r="102" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C102" s="2">
-        <v>412</v>
+        <v>406</v>
       </c>
       <c r="D102" s="2">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E102" s="2" t="s">
         <v>3975</v>
@@ -89729,7 +89777,7 @@
         <v>14</v>
       </c>
       <c r="H102" s="20" t="s">
-        <v>3953</v>
+        <v>3965</v>
       </c>
       <c r="I102" s="20" t="s">
         <v>3976</v>
@@ -89738,7 +89786,7 @@
         <v>-1</v>
       </c>
       <c r="K102" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L102" s="2">
         <v>-1</v>
@@ -89758,10 +89806,10 @@
     </row>
     <row r="103" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C103" s="2">
-        <v>413</v>
+        <v>407</v>
       </c>
       <c r="D103" s="2">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E103" s="2" t="s">
         <v>3977</v>
@@ -89773,7 +89821,7 @@
         <v>14</v>
       </c>
       <c r="H103" s="20" t="s">
-        <v>3953</v>
+        <v>3965</v>
       </c>
       <c r="I103" s="20" t="s">
         <v>3978</v>
@@ -89782,7 +89830,7 @@
         <v>-1</v>
       </c>
       <c r="K103" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L103" s="2">
         <v>-1</v>
@@ -89802,10 +89850,10 @@
     </row>
     <row r="104" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C104" s="2">
-        <v>414</v>
+        <v>408</v>
       </c>
       <c r="D104" s="2">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E104" s="2" t="s">
         <v>3979</v>
@@ -89817,7 +89865,7 @@
         <v>14</v>
       </c>
       <c r="H104" s="20" t="s">
-        <v>3953</v>
+        <v>3965</v>
       </c>
       <c r="I104" s="20" t="s">
         <v>3980</v>
@@ -89826,7 +89874,7 @@
         <v>-1</v>
       </c>
       <c r="K104" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L104" s="2">
         <v>-1</v>
@@ -89846,10 +89894,10 @@
     </row>
     <row r="105" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C105" s="2">
-        <v>415</v>
+        <v>409</v>
       </c>
       <c r="D105" s="2">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E105" s="2" t="s">
         <v>3981</v>
@@ -89861,7 +89909,7 @@
         <v>14</v>
       </c>
       <c r="H105" s="20" t="s">
-        <v>3953</v>
+        <v>3965</v>
       </c>
       <c r="I105" s="20" t="s">
         <v>3982</v>
@@ -89870,7 +89918,7 @@
         <v>-1</v>
       </c>
       <c r="K105" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L105" s="2">
         <v>-1</v>
@@ -89890,10 +89938,10 @@
     </row>
     <row r="106" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C106" s="2">
-        <v>416</v>
+        <v>410</v>
       </c>
       <c r="D106" s="2">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E106" s="2" t="s">
         <v>3983</v>
@@ -89905,7 +89953,7 @@
         <v>14</v>
       </c>
       <c r="H106" s="20" t="s">
-        <v>3953</v>
+        <v>3965</v>
       </c>
       <c r="I106" s="20" t="s">
         <v>3984</v>
@@ -89914,7 +89962,7 @@
         <v>-1</v>
       </c>
       <c r="K106" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L106" s="2">
         <v>-1</v>
@@ -89934,10 +89982,10 @@
     </row>
     <row r="107" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C107" s="2">
-        <v>417</v>
+        <v>411</v>
       </c>
       <c r="D107" s="2">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="E107" s="2" t="s">
         <v>3985</v>
@@ -89949,7 +89997,7 @@
         <v>14</v>
       </c>
       <c r="H107" s="20" t="s">
-        <v>3953</v>
+        <v>3965</v>
       </c>
       <c r="I107" s="20" t="s">
         <v>3986</v>
@@ -89958,7 +90006,7 @@
         <v>-1</v>
       </c>
       <c r="K107" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L107" s="2">
         <v>-1</v>
@@ -89978,10 +90026,10 @@
     </row>
     <row r="108" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C108" s="2">
-        <v>418</v>
+        <v>412</v>
       </c>
       <c r="D108" s="2">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E108" s="2" t="s">
         <v>3987</v>
@@ -89993,7 +90041,7 @@
         <v>14</v>
       </c>
       <c r="H108" s="20" t="s">
-        <v>3953</v>
+        <v>3965</v>
       </c>
       <c r="I108" s="20" t="s">
         <v>3988</v>
@@ -90002,7 +90050,7 @@
         <v>-1</v>
       </c>
       <c r="K108" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L108" s="2">
         <v>-1</v>
@@ -90022,10 +90070,10 @@
     </row>
     <row r="109" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C109" s="2">
-        <v>419</v>
+        <v>413</v>
       </c>
       <c r="D109" s="2">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E109" s="2" t="s">
         <v>3989</v>
@@ -90037,7 +90085,7 @@
         <v>14</v>
       </c>
       <c r="H109" s="20" t="s">
-        <v>3953</v>
+        <v>3965</v>
       </c>
       <c r="I109" s="20" t="s">
         <v>3990</v>
@@ -90066,10 +90114,10 @@
     </row>
     <row r="110" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C110" s="2">
-        <v>420</v>
+        <v>414</v>
       </c>
       <c r="D110" s="2">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="E110" s="2" t="s">
         <v>3991</v>
@@ -90081,16 +90129,16 @@
         <v>14</v>
       </c>
       <c r="H110" s="20" t="s">
+        <v>3965</v>
+      </c>
+      <c r="I110" s="20" t="s">
         <v>3992</v>
-      </c>
-      <c r="I110" s="20" t="s">
-        <v>3993</v>
       </c>
       <c r="J110" s="2">
         <v>-1</v>
       </c>
       <c r="K110" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L110" s="2">
         <v>-1</v>
@@ -90110,13 +90158,13 @@
     </row>
     <row r="111" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C111" s="2">
-        <v>421</v>
+        <v>415</v>
       </c>
       <c r="D111" s="2">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="E111" s="2" t="s">
-        <v>3994</v>
+        <v>3993</v>
       </c>
       <c r="F111" s="2">
         <v>14</v>
@@ -90125,16 +90173,16 @@
         <v>14</v>
       </c>
       <c r="H111" s="20" t="s">
-        <v>3992</v>
+        <v>3965</v>
       </c>
       <c r="I111" s="20" t="s">
-        <v>3995</v>
+        <v>3994</v>
       </c>
       <c r="J111" s="2">
         <v>-1</v>
       </c>
       <c r="K111" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L111" s="2">
         <v>-1</v>
@@ -90154,13 +90202,13 @@
     </row>
     <row r="112" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C112" s="2">
-        <v>422</v>
+        <v>416</v>
       </c>
       <c r="D112" s="2">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="E112" s="2" t="s">
-        <v>3996</v>
+        <v>3995</v>
       </c>
       <c r="F112" s="2">
         <v>14</v>
@@ -90169,16 +90217,16 @@
         <v>14</v>
       </c>
       <c r="H112" s="20" t="s">
-        <v>3997</v>
+        <v>3965</v>
       </c>
       <c r="I112" s="20" t="s">
-        <v>3998</v>
+        <v>3996</v>
       </c>
       <c r="J112" s="2">
         <v>-1</v>
       </c>
       <c r="K112" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L112" s="2">
         <v>-1</v>
@@ -90198,13 +90246,13 @@
     </row>
     <row r="113" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C113" s="2">
-        <v>423</v>
+        <v>417</v>
       </c>
       <c r="D113" s="2">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="E113" s="2" t="s">
-        <v>3999</v>
+        <v>3997</v>
       </c>
       <c r="F113" s="2">
         <v>14</v>
@@ -90213,16 +90261,16 @@
         <v>14</v>
       </c>
       <c r="H113" s="20" t="s">
-        <v>4000</v>
+        <v>3965</v>
       </c>
       <c r="I113" s="20" t="s">
-        <v>4001</v>
+        <v>3998</v>
       </c>
       <c r="J113" s="2">
         <v>-1</v>
       </c>
       <c r="K113" s="2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L113" s="2">
         <v>-1</v>
@@ -90242,13 +90290,13 @@
     </row>
     <row r="114" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C114" s="2">
-        <v>424</v>
+        <v>418</v>
       </c>
       <c r="D114" s="2">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="E114" s="2" t="s">
-        <v>4002</v>
+        <v>3999</v>
       </c>
       <c r="F114" s="2">
         <v>14</v>
@@ -90257,16 +90305,16 @@
         <v>14</v>
       </c>
       <c r="H114" s="20" t="s">
+        <v>3965</v>
+      </c>
+      <c r="I114" s="20" t="s">
         <v>4000</v>
-      </c>
-      <c r="I114" s="20" t="s">
-        <v>4003</v>
       </c>
       <c r="J114" s="2">
         <v>-1</v>
       </c>
       <c r="K114" s="2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L114" s="2">
         <v>-1</v>
@@ -90284,20 +90332,372 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" customHeight="1" spans="9:9">
-      <c r="I121" s="9"/>
-    </row>
-    <row r="122" customHeight="1" spans="9:9">
-      <c r="I122" s="9"/>
-    </row>
-    <row r="123" customHeight="1" spans="9:9">
-      <c r="I123" s="9"/>
-    </row>
-    <row r="124" customHeight="1" spans="9:9">
-      <c r="I124" s="9"/>
-    </row>
-    <row r="125" customHeight="1" spans="9:9">
-      <c r="I125" s="9"/>
+    <row r="115" s="2" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C115" s="2">
+        <v>419</v>
+      </c>
+      <c r="D115" s="2">
+        <v>19</v>
+      </c>
+      <c r="E115" s="2" t="s">
+        <v>4001</v>
+      </c>
+      <c r="F115" s="2">
+        <v>14</v>
+      </c>
+      <c r="G115" s="2">
+        <v>14</v>
+      </c>
+      <c r="H115" s="20" t="s">
+        <v>3965</v>
+      </c>
+      <c r="I115" s="20" t="s">
+        <v>4002</v>
+      </c>
+      <c r="J115" s="2">
+        <v>-1</v>
+      </c>
+      <c r="K115" s="2">
+        <v>5</v>
+      </c>
+      <c r="L115" s="2">
+        <v>-1</v>
+      </c>
+      <c r="M115" s="2">
+        <v>-1</v>
+      </c>
+      <c r="N115" s="2">
+        <v>1</v>
+      </c>
+      <c r="O115" s="2">
+        <v>0</v>
+      </c>
+      <c r="P115" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116" s="2" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C116" s="2">
+        <v>420</v>
+      </c>
+      <c r="D116" s="2">
+        <v>20</v>
+      </c>
+      <c r="E116" s="2" t="s">
+        <v>4003</v>
+      </c>
+      <c r="F116" s="2">
+        <v>14</v>
+      </c>
+      <c r="G116" s="2">
+        <v>14</v>
+      </c>
+      <c r="H116" s="20" t="s">
+        <v>4004</v>
+      </c>
+      <c r="I116" s="20" t="s">
+        <v>4005</v>
+      </c>
+      <c r="J116" s="2">
+        <v>-1</v>
+      </c>
+      <c r="K116" s="2">
+        <v>6</v>
+      </c>
+      <c r="L116" s="2">
+        <v>-1</v>
+      </c>
+      <c r="M116" s="2">
+        <v>-1</v>
+      </c>
+      <c r="N116" s="2">
+        <v>1</v>
+      </c>
+      <c r="O116" s="2">
+        <v>0</v>
+      </c>
+      <c r="P116" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117" s="2" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C117" s="2">
+        <v>421</v>
+      </c>
+      <c r="D117" s="2">
+        <v>21</v>
+      </c>
+      <c r="E117" s="2" t="s">
+        <v>4006</v>
+      </c>
+      <c r="F117" s="2">
+        <v>14</v>
+      </c>
+      <c r="G117" s="2">
+        <v>14</v>
+      </c>
+      <c r="H117" s="20" t="s">
+        <v>4004</v>
+      </c>
+      <c r="I117" s="20" t="s">
+        <v>4007</v>
+      </c>
+      <c r="J117" s="2">
+        <v>-1</v>
+      </c>
+      <c r="K117" s="2">
+        <v>6</v>
+      </c>
+      <c r="L117" s="2">
+        <v>-1</v>
+      </c>
+      <c r="M117" s="2">
+        <v>-1</v>
+      </c>
+      <c r="N117" s="2">
+        <v>1</v>
+      </c>
+      <c r="O117" s="2">
+        <v>0</v>
+      </c>
+      <c r="P117" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118" s="2" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C118" s="2">
+        <v>422</v>
+      </c>
+      <c r="D118" s="2">
+        <v>22</v>
+      </c>
+      <c r="E118" s="2" t="s">
+        <v>4008</v>
+      </c>
+      <c r="F118" s="2">
+        <v>14</v>
+      </c>
+      <c r="G118" s="2">
+        <v>14</v>
+      </c>
+      <c r="H118" s="20" t="s">
+        <v>4009</v>
+      </c>
+      <c r="I118" s="20" t="s">
+        <v>4010</v>
+      </c>
+      <c r="J118" s="2">
+        <v>-1</v>
+      </c>
+      <c r="K118" s="2">
+        <v>6</v>
+      </c>
+      <c r="L118" s="2">
+        <v>-1</v>
+      </c>
+      <c r="M118" s="2">
+        <v>-1</v>
+      </c>
+      <c r="N118" s="2">
+        <v>1</v>
+      </c>
+      <c r="O118" s="2">
+        <v>0</v>
+      </c>
+      <c r="P118" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119" s="2" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C119" s="2">
+        <v>423</v>
+      </c>
+      <c r="D119" s="2">
+        <v>23</v>
+      </c>
+      <c r="E119" s="2" t="s">
+        <v>4011</v>
+      </c>
+      <c r="F119" s="2">
+        <v>14</v>
+      </c>
+      <c r="G119" s="2">
+        <v>14</v>
+      </c>
+      <c r="H119" s="20" t="s">
+        <v>4012</v>
+      </c>
+      <c r="I119" s="20" t="s">
+        <v>4013</v>
+      </c>
+      <c r="J119" s="2">
+        <v>-1</v>
+      </c>
+      <c r="K119" s="2">
+        <v>7</v>
+      </c>
+      <c r="L119" s="2">
+        <v>-1</v>
+      </c>
+      <c r="M119" s="2">
+        <v>-1</v>
+      </c>
+      <c r="N119" s="2">
+        <v>1</v>
+      </c>
+      <c r="O119" s="2">
+        <v>0</v>
+      </c>
+      <c r="P119" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120" s="2" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C120" s="2">
+        <v>424</v>
+      </c>
+      <c r="D120" s="2">
+        <v>24</v>
+      </c>
+      <c r="E120" s="2" t="s">
+        <v>4014</v>
+      </c>
+      <c r="F120" s="2">
+        <v>14</v>
+      </c>
+      <c r="G120" s="2">
+        <v>14</v>
+      </c>
+      <c r="H120" s="20" t="s">
+        <v>4012</v>
+      </c>
+      <c r="I120" s="20" t="s">
+        <v>4015</v>
+      </c>
+      <c r="J120" s="2">
+        <v>-1</v>
+      </c>
+      <c r="K120" s="2">
+        <v>7</v>
+      </c>
+      <c r="L120" s="2">
+        <v>-1</v>
+      </c>
+      <c r="M120" s="2">
+        <v>-1</v>
+      </c>
+      <c r="N120" s="2">
+        <v>1</v>
+      </c>
+      <c r="O120" s="2">
+        <v>0</v>
+      </c>
+      <c r="P120" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121" s="2" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C121" s="2">
+        <v>425</v>
+      </c>
+      <c r="D121" s="2">
+        <v>25</v>
+      </c>
+      <c r="E121" s="2" t="s">
+        <v>4016</v>
+      </c>
+      <c r="F121" s="2">
+        <v>14</v>
+      </c>
+      <c r="G121" s="2">
+        <v>14</v>
+      </c>
+      <c r="H121" s="20" t="s">
+        <v>4012</v>
+      </c>
+      <c r="I121" s="20" t="s">
+        <v>4017</v>
+      </c>
+      <c r="J121" s="2">
+        <v>-1</v>
+      </c>
+      <c r="K121" s="2">
+        <v>7</v>
+      </c>
+      <c r="L121" s="2">
+        <v>-1</v>
+      </c>
+      <c r="M121" s="2">
+        <v>-1</v>
+      </c>
+      <c r="N121" s="2">
+        <v>1</v>
+      </c>
+      <c r="O121" s="2">
+        <v>0</v>
+      </c>
+      <c r="P121" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122" s="2" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C122" s="2">
+        <v>426</v>
+      </c>
+      <c r="D122" s="2">
+        <v>26</v>
+      </c>
+      <c r="E122" s="2" t="s">
+        <v>4018</v>
+      </c>
+      <c r="F122" s="2">
+        <v>14</v>
+      </c>
+      <c r="G122" s="2">
+        <v>14</v>
+      </c>
+      <c r="H122" s="20" t="s">
+        <v>4012</v>
+      </c>
+      <c r="I122" s="20" t="s">
+        <v>4019</v>
+      </c>
+      <c r="J122" s="2">
+        <v>-1</v>
+      </c>
+      <c r="K122" s="2">
+        <v>7</v>
+      </c>
+      <c r="L122" s="2">
+        <v>-1</v>
+      </c>
+      <c r="M122" s="2">
+        <v>-1</v>
+      </c>
+      <c r="N122" s="2">
+        <v>1</v>
+      </c>
+      <c r="O122" s="2">
+        <v>0</v>
+      </c>
+      <c r="P122" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127" customHeight="1" spans="9:9">
+      <c r="I127" s="9"/>
+    </row>
+    <row r="128" customHeight="1" spans="9:9">
+      <c r="I128" s="9"/>
+    </row>
+    <row r="129" customHeight="1" spans="9:9">
+      <c r="I129" s="9"/>
+    </row>
+    <row r="130" customHeight="1" spans="9:9">
+      <c r="I130" s="9"/>
+    </row>
+    <row r="131" customHeight="1" spans="9:9">
+      <c r="I131" s="9"/>
     </row>
   </sheetData>
   <dataValidations count="1">

--- a/Excel/EquipConfig.xlsx
+++ b/Excel/EquipConfig.xlsx
@@ -11704,13 +11704,13 @@
     <t>斗笠二五阶</t>
   </si>
   <si>
-    <t>2400,2400,2400,2400,90,600</t>
+    <t>2400,2400,2400,2400,100,600</t>
   </si>
   <si>
     <t>斗笠二六阶</t>
   </si>
   <si>
-    <t>3000,3000,3000,3000,100,800</t>
+    <t>3000,3000,3000,3000,120,800</t>
   </si>
   <si>
     <t>护盾一阶</t>

--- a/Excel/EquipConfig.xlsx
+++ b/Excel/EquipConfig.xlsx
@@ -143,7 +143,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21430" uniqueCount="4020">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21430" uniqueCount="4024">
   <si>
     <t>_id</t>
   </si>
@@ -11710,7 +11710,10 @@
     <t>斗笠二六阶</t>
   </si>
   <si>
-    <t>3000,3000,3000,3000,120,800</t>
+    <t>26,27,28,12,2010,20,53</t>
+  </si>
+  <si>
+    <t>3000,3000,3000,3000,120,800,1</t>
   </si>
   <si>
     <t>护盾一阶</t>
@@ -11872,7 +11875,10 @@
     <t>护盾二六阶</t>
   </si>
   <si>
-    <t>3000,3000,3000,60,120,800</t>
+    <t>15,16,13,2011,2002,19,51</t>
+  </si>
+  <si>
+    <t>3000,3000,3000,60,120,800,1</t>
   </si>
   <si>
     <t>神符一阶</t>
@@ -12034,7 +12040,10 @@
     <t>神符二六阶</t>
   </si>
   <si>
-    <t>300,100,3000,3000,3000,120</t>
+    <t>7,8,14,18,20,2001,52</t>
+  </si>
+  <si>
+    <t>300,100,3000,3000,3000,120,1</t>
   </si>
   <si>
     <t>魔石一阶</t>
@@ -12202,7 +12211,10 @@
     <t>魔石二六阶</t>
   </si>
   <si>
-    <t>100,3000,6,200,200,800</t>
+    <t>10,15,23,2003,2002,24,50</t>
+  </si>
+  <si>
+    <t>100,3000,6,200,200,800,1</t>
   </si>
 </sst>
 </file>
@@ -87210,10 +87222,10 @@
         <v>11</v>
       </c>
       <c r="H39" s="20" t="s">
-        <v>3848</v>
+        <v>3855</v>
       </c>
       <c r="I39" s="22" t="s">
-        <v>3855</v>
+        <v>3856</v>
       </c>
       <c r="J39" s="2">
         <v>-1</v>
@@ -87251,7 +87263,7 @@
         <v>1</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>3856</v>
+        <v>3857</v>
       </c>
       <c r="F42" s="2">
         <v>12</v>
@@ -87260,10 +87272,10 @@
         <v>12</v>
       </c>
       <c r="H42" s="20" t="s">
-        <v>3857</v>
+        <v>3858</v>
       </c>
       <c r="I42" s="20" t="s">
-        <v>3858</v>
+        <v>3859</v>
       </c>
       <c r="J42" s="2">
         <v>-1</v>
@@ -87295,7 +87307,7 @@
         <v>2</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>3859</v>
+        <v>3860</v>
       </c>
       <c r="F43" s="2">
         <v>12</v>
@@ -87304,10 +87316,10 @@
         <v>12</v>
       </c>
       <c r="H43" s="20" t="s">
-        <v>3857</v>
+        <v>3858</v>
       </c>
       <c r="I43" s="20" t="s">
-        <v>3860</v>
+        <v>3861</v>
       </c>
       <c r="J43" s="2">
         <v>-1</v>
@@ -87339,7 +87351,7 @@
         <v>3</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>3861</v>
+        <v>3862</v>
       </c>
       <c r="F44" s="2">
         <v>12</v>
@@ -87348,10 +87360,10 @@
         <v>12</v>
       </c>
       <c r="H44" s="20" t="s">
-        <v>3857</v>
+        <v>3858</v>
       </c>
       <c r="I44" s="22" t="s">
-        <v>3862</v>
+        <v>3863</v>
       </c>
       <c r="J44" s="2">
         <v>-1</v>
@@ -87383,7 +87395,7 @@
         <v>4</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>3863</v>
+        <v>3864</v>
       </c>
       <c r="F45" s="2">
         <v>12</v>
@@ -87392,10 +87404,10 @@
         <v>12</v>
       </c>
       <c r="H45" s="20" t="s">
-        <v>3857</v>
+        <v>3858</v>
       </c>
       <c r="I45" s="22" t="s">
-        <v>3864</v>
+        <v>3865</v>
       </c>
       <c r="J45" s="2">
         <v>-1</v>
@@ -87427,7 +87439,7 @@
         <v>5</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>3865</v>
+        <v>3866</v>
       </c>
       <c r="F46" s="2">
         <v>12</v>
@@ -87436,7 +87448,7 @@
         <v>12</v>
       </c>
       <c r="H46" s="20" t="s">
-        <v>3857</v>
+        <v>3858</v>
       </c>
       <c r="I46" s="22" t="s">
         <v>3794</v>
@@ -87471,7 +87483,7 @@
         <v>6</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>3866</v>
+        <v>3867</v>
       </c>
       <c r="F47" s="2">
         <v>12</v>
@@ -87480,10 +87492,10 @@
         <v>12</v>
       </c>
       <c r="H47" s="20" t="s">
-        <v>3857</v>
+        <v>3858</v>
       </c>
       <c r="I47" s="22" t="s">
-        <v>3867</v>
+        <v>3868</v>
       </c>
       <c r="J47" s="2">
         <v>-1</v>
@@ -87515,7 +87527,7 @@
         <v>7</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>3868</v>
+        <v>3869</v>
       </c>
       <c r="F48" s="2">
         <v>12</v>
@@ -87524,10 +87536,10 @@
         <v>12</v>
       </c>
       <c r="H48" s="20" t="s">
-        <v>3857</v>
+        <v>3858</v>
       </c>
       <c r="I48" s="22" t="s">
-        <v>3869</v>
+        <v>3870</v>
       </c>
       <c r="J48" s="2">
         <v>-1</v>
@@ -87559,7 +87571,7 @@
         <v>8</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>3870</v>
+        <v>3871</v>
       </c>
       <c r="F49" s="2">
         <v>12</v>
@@ -87568,10 +87580,10 @@
         <v>12</v>
       </c>
       <c r="H49" s="20" t="s">
-        <v>3857</v>
+        <v>3858</v>
       </c>
       <c r="I49" s="22" t="s">
-        <v>3871</v>
+        <v>3872</v>
       </c>
       <c r="J49" s="2">
         <v>-1</v>
@@ -87603,7 +87615,7 @@
         <v>9</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>3872</v>
+        <v>3873</v>
       </c>
       <c r="F50" s="2">
         <v>12</v>
@@ -87612,10 +87624,10 @@
         <v>12</v>
       </c>
       <c r="H50" s="20" t="s">
-        <v>3857</v>
+        <v>3858</v>
       </c>
       <c r="I50" s="22" t="s">
-        <v>3873</v>
+        <v>3874</v>
       </c>
       <c r="J50" s="2">
         <v>-1</v>
@@ -87647,7 +87659,7 @@
         <v>10</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>3874</v>
+        <v>3875</v>
       </c>
       <c r="F51" s="2">
         <v>12</v>
@@ -87656,7 +87668,7 @@
         <v>12</v>
       </c>
       <c r="H51" s="20" t="s">
-        <v>3857</v>
+        <v>3858</v>
       </c>
       <c r="I51" s="22" t="s">
         <v>3791</v>
@@ -87691,7 +87703,7 @@
         <v>11</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>3875</v>
+        <v>3876</v>
       </c>
       <c r="F52" s="2">
         <v>12</v>
@@ -87700,10 +87712,10 @@
         <v>12</v>
       </c>
       <c r="H52" s="20" t="s">
-        <v>3857</v>
+        <v>3858</v>
       </c>
       <c r="I52" s="22" t="s">
-        <v>3876</v>
+        <v>3877</v>
       </c>
       <c r="J52" s="2">
         <v>-1</v>
@@ -87735,7 +87747,7 @@
         <v>12</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>3877</v>
+        <v>3878</v>
       </c>
       <c r="F53" s="2">
         <v>12</v>
@@ -87744,10 +87756,10 @@
         <v>12</v>
       </c>
       <c r="H53" s="20" t="s">
-        <v>3857</v>
+        <v>3858</v>
       </c>
       <c r="I53" s="22" t="s">
-        <v>3878</v>
+        <v>3879</v>
       </c>
       <c r="J53" s="2">
         <v>-1</v>
@@ -87779,7 +87791,7 @@
         <v>13</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>3879</v>
+        <v>3880</v>
       </c>
       <c r="F54" s="2">
         <v>12</v>
@@ -87788,10 +87800,10 @@
         <v>12</v>
       </c>
       <c r="H54" s="20" t="s">
-        <v>3857</v>
+        <v>3858</v>
       </c>
       <c r="I54" s="22" t="s">
-        <v>3880</v>
+        <v>3881</v>
       </c>
       <c r="J54" s="2">
         <v>-1</v>
@@ -87823,7 +87835,7 @@
         <v>14</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>3881</v>
+        <v>3882</v>
       </c>
       <c r="F55" s="2">
         <v>12</v>
@@ -87832,10 +87844,10 @@
         <v>12</v>
       </c>
       <c r="H55" s="20" t="s">
-        <v>3857</v>
+        <v>3858</v>
       </c>
       <c r="I55" s="22" t="s">
-        <v>3882</v>
+        <v>3883</v>
       </c>
       <c r="J55" s="2">
         <v>-1</v>
@@ -87867,7 +87879,7 @@
         <v>15</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>3883</v>
+        <v>3884</v>
       </c>
       <c r="F56" s="2">
         <v>12</v>
@@ -87876,10 +87888,10 @@
         <v>12</v>
       </c>
       <c r="H56" s="20" t="s">
-        <v>3857</v>
+        <v>3858</v>
       </c>
       <c r="I56" s="22" t="s">
-        <v>3884</v>
+        <v>3885</v>
       </c>
       <c r="J56" s="2">
         <v>-1</v>
@@ -87911,7 +87923,7 @@
         <v>16</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>3885</v>
+        <v>3886</v>
       </c>
       <c r="F57" s="2">
         <v>12</v>
@@ -87920,10 +87932,10 @@
         <v>12</v>
       </c>
       <c r="H57" s="20" t="s">
-        <v>3857</v>
+        <v>3858</v>
       </c>
       <c r="I57" s="22" t="s">
-        <v>3886</v>
+        <v>3887</v>
       </c>
       <c r="J57" s="2">
         <v>-1</v>
@@ -87955,7 +87967,7 @@
         <v>17</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>3887</v>
+        <v>3888</v>
       </c>
       <c r="F58" s="2">
         <v>12</v>
@@ -87964,10 +87976,10 @@
         <v>12</v>
       </c>
       <c r="H58" s="20" t="s">
-        <v>3857</v>
+        <v>3858</v>
       </c>
       <c r="I58" s="22" t="s">
-        <v>3888</v>
+        <v>3889</v>
       </c>
       <c r="J58" s="2">
         <v>-1</v>
@@ -87999,7 +88011,7 @@
         <v>18</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>3889</v>
+        <v>3890</v>
       </c>
       <c r="F59" s="2">
         <v>12</v>
@@ -88008,10 +88020,10 @@
         <v>12</v>
       </c>
       <c r="H59" s="20" t="s">
-        <v>3857</v>
+        <v>3858</v>
       </c>
       <c r="I59" s="22" t="s">
-        <v>3890</v>
+        <v>3891</v>
       </c>
       <c r="J59" s="2">
         <v>-1</v>
@@ -88043,7 +88055,7 @@
         <v>19</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>3891</v>
+        <v>3892</v>
       </c>
       <c r="F60" s="2">
         <v>12</v>
@@ -88052,10 +88064,10 @@
         <v>12</v>
       </c>
       <c r="H60" s="20" t="s">
-        <v>3857</v>
+        <v>3858</v>
       </c>
       <c r="I60" s="22" t="s">
-        <v>3892</v>
+        <v>3893</v>
       </c>
       <c r="J60" s="2">
         <v>-1</v>
@@ -88087,7 +88099,7 @@
         <v>20</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>3893</v>
+        <v>3894</v>
       </c>
       <c r="F61" s="2">
         <v>12</v>
@@ -88096,10 +88108,10 @@
         <v>12</v>
       </c>
       <c r="H61" s="20" t="s">
-        <v>3894</v>
+        <v>3895</v>
       </c>
       <c r="I61" s="22" t="s">
-        <v>3895</v>
+        <v>3896</v>
       </c>
       <c r="J61" s="2">
         <v>-1</v>
@@ -88131,7 +88143,7 @@
         <v>21</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>3896</v>
+        <v>3897</v>
       </c>
       <c r="F62" s="2">
         <v>12</v>
@@ -88140,10 +88152,10 @@
         <v>12</v>
       </c>
       <c r="H62" s="20" t="s">
-        <v>3894</v>
+        <v>3895</v>
       </c>
       <c r="I62" s="22" t="s">
-        <v>3897</v>
+        <v>3898</v>
       </c>
       <c r="J62" s="2">
         <v>-1</v>
@@ -88175,7 +88187,7 @@
         <v>22</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>3898</v>
+        <v>3899</v>
       </c>
       <c r="F63" s="2">
         <v>12</v>
@@ -88184,10 +88196,10 @@
         <v>12</v>
       </c>
       <c r="H63" s="20" t="s">
-        <v>3899</v>
+        <v>3900</v>
       </c>
       <c r="I63" s="22" t="s">
-        <v>3900</v>
+        <v>3901</v>
       </c>
       <c r="J63" s="2">
         <v>-1</v>
@@ -88219,7 +88231,7 @@
         <v>23</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>3901</v>
+        <v>3902</v>
       </c>
       <c r="F64" s="2">
         <v>12</v>
@@ -88228,10 +88240,10 @@
         <v>12</v>
       </c>
       <c r="H64" s="20" t="s">
-        <v>3902</v>
+        <v>3903</v>
       </c>
       <c r="I64" s="22" t="s">
-        <v>3903</v>
+        <v>3904</v>
       </c>
       <c r="J64" s="2">
         <v>-1</v>
@@ -88263,7 +88275,7 @@
         <v>24</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>3904</v>
+        <v>3905</v>
       </c>
       <c r="F65" s="2">
         <v>12</v>
@@ -88272,10 +88284,10 @@
         <v>12</v>
       </c>
       <c r="H65" s="20" t="s">
-        <v>3902</v>
+        <v>3903</v>
       </c>
       <c r="I65" s="22" t="s">
-        <v>3905</v>
+        <v>3906</v>
       </c>
       <c r="J65" s="2">
         <v>-1</v>
@@ -88307,7 +88319,7 @@
         <v>25</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>3906</v>
+        <v>3907</v>
       </c>
       <c r="F66" s="2">
         <v>12</v>
@@ -88316,10 +88328,10 @@
         <v>12</v>
       </c>
       <c r="H66" s="20" t="s">
-        <v>3902</v>
+        <v>3903</v>
       </c>
       <c r="I66" s="22" t="s">
-        <v>3907</v>
+        <v>3908</v>
       </c>
       <c r="J66" s="2">
         <v>-1</v>
@@ -88351,7 +88363,7 @@
         <v>26</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>3908</v>
+        <v>3909</v>
       </c>
       <c r="F67" s="2">
         <v>12</v>
@@ -88360,10 +88372,10 @@
         <v>12</v>
       </c>
       <c r="H67" s="20" t="s">
-        <v>3902</v>
+        <v>3910</v>
       </c>
       <c r="I67" s="22" t="s">
-        <v>3909</v>
+        <v>3911</v>
       </c>
       <c r="J67" s="2">
         <v>-1</v>
@@ -88398,7 +88410,7 @@
         <v>1</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>3910</v>
+        <v>3912</v>
       </c>
       <c r="F69" s="2">
         <v>13</v>
@@ -88407,10 +88419,10 @@
         <v>13</v>
       </c>
       <c r="H69" s="20" t="s">
-        <v>3911</v>
+        <v>3913</v>
       </c>
       <c r="I69" s="22" t="s">
-        <v>3912</v>
+        <v>3914</v>
       </c>
       <c r="J69" s="2">
         <v>-1</v>
@@ -88442,7 +88454,7 @@
         <v>2</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>3913</v>
+        <v>3915</v>
       </c>
       <c r="F70" s="2">
         <v>13</v>
@@ -88451,10 +88463,10 @@
         <v>13</v>
       </c>
       <c r="H70" s="20" t="s">
-        <v>3911</v>
+        <v>3913</v>
       </c>
       <c r="I70" s="22" t="s">
-        <v>3914</v>
+        <v>3916</v>
       </c>
       <c r="J70" s="2">
         <v>-1</v>
@@ -88486,7 +88498,7 @@
         <v>3</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>3915</v>
+        <v>3917</v>
       </c>
       <c r="F71" s="2">
         <v>13</v>
@@ -88495,10 +88507,10 @@
         <v>13</v>
       </c>
       <c r="H71" s="20" t="s">
-        <v>3911</v>
+        <v>3913</v>
       </c>
       <c r="I71" s="22" t="s">
-        <v>3916</v>
+        <v>3918</v>
       </c>
       <c r="J71" s="2">
         <v>-1</v>
@@ -88530,7 +88542,7 @@
         <v>4</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>3917</v>
+        <v>3919</v>
       </c>
       <c r="F72" s="2">
         <v>13</v>
@@ -88539,10 +88551,10 @@
         <v>13</v>
       </c>
       <c r="H72" s="20" t="s">
-        <v>3911</v>
+        <v>3913</v>
       </c>
       <c r="I72" s="22" t="s">
-        <v>3918</v>
+        <v>3920</v>
       </c>
       <c r="J72" s="2">
         <v>-1</v>
@@ -88574,7 +88586,7 @@
         <v>5</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>3919</v>
+        <v>3921</v>
       </c>
       <c r="F73" s="2">
         <v>13</v>
@@ -88583,10 +88595,10 @@
         <v>13</v>
       </c>
       <c r="H73" s="20" t="s">
-        <v>3911</v>
+        <v>3913</v>
       </c>
       <c r="I73" s="22" t="s">
-        <v>3920</v>
+        <v>3922</v>
       </c>
       <c r="J73" s="2">
         <v>-1</v>
@@ -88618,7 +88630,7 @@
         <v>6</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>3921</v>
+        <v>3923</v>
       </c>
       <c r="F74" s="2">
         <v>13</v>
@@ -88627,10 +88639,10 @@
         <v>13</v>
       </c>
       <c r="H74" s="20" t="s">
-        <v>3911</v>
+        <v>3913</v>
       </c>
       <c r="I74" s="22" t="s">
-        <v>3922</v>
+        <v>3924</v>
       </c>
       <c r="J74" s="2">
         <v>-1</v>
@@ -88662,7 +88674,7 @@
         <v>7</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>3923</v>
+        <v>3925</v>
       </c>
       <c r="F75" s="2">
         <v>13</v>
@@ -88671,10 +88683,10 @@
         <v>13</v>
       </c>
       <c r="H75" s="20" t="s">
-        <v>3911</v>
+        <v>3913</v>
       </c>
       <c r="I75" s="22" t="s">
-        <v>3924</v>
+        <v>3926</v>
       </c>
       <c r="J75" s="2">
         <v>-1</v>
@@ -88706,7 +88718,7 @@
         <v>8</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>3925</v>
+        <v>3927</v>
       </c>
       <c r="F76" s="2">
         <v>13</v>
@@ -88715,10 +88727,10 @@
         <v>13</v>
       </c>
       <c r="H76" s="20" t="s">
-        <v>3911</v>
+        <v>3913</v>
       </c>
       <c r="I76" s="22" t="s">
-        <v>3926</v>
+        <v>3928</v>
       </c>
       <c r="J76" s="2">
         <v>-1</v>
@@ -88750,7 +88762,7 @@
         <v>9</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>3927</v>
+        <v>3929</v>
       </c>
       <c r="F77" s="2">
         <v>13</v>
@@ -88759,10 +88771,10 @@
         <v>13</v>
       </c>
       <c r="H77" s="20" t="s">
-        <v>3911</v>
+        <v>3913</v>
       </c>
       <c r="I77" s="22" t="s">
-        <v>3928</v>
+        <v>3930</v>
       </c>
       <c r="J77" s="2">
         <v>-1</v>
@@ -88794,7 +88806,7 @@
         <v>10</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>3929</v>
+        <v>3931</v>
       </c>
       <c r="F78" s="2">
         <v>13</v>
@@ -88803,10 +88815,10 @@
         <v>13</v>
       </c>
       <c r="H78" s="20" t="s">
-        <v>3911</v>
+        <v>3913</v>
       </c>
       <c r="I78" s="22" t="s">
-        <v>3930</v>
+        <v>3932</v>
       </c>
       <c r="J78" s="2">
         <v>-1</v>
@@ -88838,7 +88850,7 @@
         <v>11</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>3931</v>
+        <v>3933</v>
       </c>
       <c r="F79" s="2">
         <v>13</v>
@@ -88847,10 +88859,10 @@
         <v>13</v>
       </c>
       <c r="H79" s="20" t="s">
-        <v>3911</v>
+        <v>3913</v>
       </c>
       <c r="I79" s="22" t="s">
-        <v>3932</v>
+        <v>3934</v>
       </c>
       <c r="J79" s="2">
         <v>-1</v>
@@ -88882,7 +88894,7 @@
         <v>12</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>3933</v>
+        <v>3935</v>
       </c>
       <c r="F80" s="2">
         <v>13</v>
@@ -88891,10 +88903,10 @@
         <v>13</v>
       </c>
       <c r="H80" s="20" t="s">
-        <v>3911</v>
+        <v>3913</v>
       </c>
       <c r="I80" s="22" t="s">
-        <v>3934</v>
+        <v>3936</v>
       </c>
       <c r="J80" s="2">
         <v>-1</v>
@@ -88926,7 +88938,7 @@
         <v>13</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>3935</v>
+        <v>3937</v>
       </c>
       <c r="F81" s="2">
         <v>13</v>
@@ -88935,10 +88947,10 @@
         <v>13</v>
       </c>
       <c r="H81" s="20" t="s">
-        <v>3911</v>
+        <v>3913</v>
       </c>
       <c r="I81" s="22" t="s">
-        <v>3936</v>
+        <v>3938</v>
       </c>
       <c r="J81" s="2">
         <v>-1</v>
@@ -88970,7 +88982,7 @@
         <v>14</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>3937</v>
+        <v>3939</v>
       </c>
       <c r="F82" s="2">
         <v>13</v>
@@ -88979,10 +88991,10 @@
         <v>13</v>
       </c>
       <c r="H82" s="20" t="s">
-        <v>3911</v>
+        <v>3913</v>
       </c>
       <c r="I82" s="22" t="s">
-        <v>3938</v>
+        <v>3940</v>
       </c>
       <c r="J82" s="2">
         <v>-1</v>
@@ -89014,7 +89026,7 @@
         <v>15</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>3939</v>
+        <v>3941</v>
       </c>
       <c r="F83" s="2">
         <v>13</v>
@@ -89023,10 +89035,10 @@
         <v>13</v>
       </c>
       <c r="H83" s="20" t="s">
-        <v>3911</v>
+        <v>3913</v>
       </c>
       <c r="I83" s="22" t="s">
-        <v>3940</v>
+        <v>3942</v>
       </c>
       <c r="J83" s="2">
         <v>-1</v>
@@ -89058,7 +89070,7 @@
         <v>16</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>3941</v>
+        <v>3943</v>
       </c>
       <c r="F84" s="2">
         <v>13</v>
@@ -89067,10 +89079,10 @@
         <v>13</v>
       </c>
       <c r="H84" s="20" t="s">
-        <v>3911</v>
+        <v>3913</v>
       </c>
       <c r="I84" s="22" t="s">
-        <v>3942</v>
+        <v>3944</v>
       </c>
       <c r="J84" s="2">
         <v>-1</v>
@@ -89102,7 +89114,7 @@
         <v>17</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>3943</v>
+        <v>3945</v>
       </c>
       <c r="F85" s="2">
         <v>13</v>
@@ -89111,10 +89123,10 @@
         <v>13</v>
       </c>
       <c r="H85" s="20" t="s">
-        <v>3911</v>
+        <v>3913</v>
       </c>
       <c r="I85" s="22" t="s">
-        <v>3944</v>
+        <v>3946</v>
       </c>
       <c r="J85" s="2">
         <v>-1</v>
@@ -89146,7 +89158,7 @@
         <v>18</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>3945</v>
+        <v>3947</v>
       </c>
       <c r="F86" s="2">
         <v>13</v>
@@ -89155,10 +89167,10 @@
         <v>13</v>
       </c>
       <c r="H86" s="20" t="s">
-        <v>3911</v>
+        <v>3913</v>
       </c>
       <c r="I86" s="22" t="s">
-        <v>3946</v>
+        <v>3948</v>
       </c>
       <c r="J86" s="2">
         <v>-1</v>
@@ -89190,7 +89202,7 @@
         <v>19</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>3947</v>
+        <v>3949</v>
       </c>
       <c r="F87" s="2">
         <v>13</v>
@@ -89199,10 +89211,10 @@
         <v>13</v>
       </c>
       <c r="H87" s="20" t="s">
-        <v>3911</v>
+        <v>3913</v>
       </c>
       <c r="I87" s="22" t="s">
-        <v>3948</v>
+        <v>3950</v>
       </c>
       <c r="J87" s="2">
         <v>-1</v>
@@ -89234,7 +89246,7 @@
         <v>20</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>3949</v>
+        <v>3951</v>
       </c>
       <c r="F88" s="2">
         <v>13</v>
@@ -89243,10 +89255,10 @@
         <v>13</v>
       </c>
       <c r="H88" s="20" t="s">
-        <v>3950</v>
+        <v>3952</v>
       </c>
       <c r="I88" s="22" t="s">
-        <v>3951</v>
+        <v>3953</v>
       </c>
       <c r="J88" s="2">
         <v>-1</v>
@@ -89278,7 +89290,7 @@
         <v>21</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>3952</v>
+        <v>3954</v>
       </c>
       <c r="F89" s="2">
         <v>13</v>
@@ -89287,10 +89299,10 @@
         <v>13</v>
       </c>
       <c r="H89" s="20" t="s">
-        <v>3950</v>
+        <v>3952</v>
       </c>
       <c r="I89" s="22" t="s">
-        <v>3953</v>
+        <v>3955</v>
       </c>
       <c r="J89" s="2">
         <v>-1</v>
@@ -89322,7 +89334,7 @@
         <v>22</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>3954</v>
+        <v>3956</v>
       </c>
       <c r="F90" s="2">
         <v>13</v>
@@ -89331,10 +89343,10 @@
         <v>13</v>
       </c>
       <c r="H90" s="20" t="s">
-        <v>3950</v>
+        <v>3952</v>
       </c>
       <c r="I90" s="22" t="s">
-        <v>3955</v>
+        <v>3957</v>
       </c>
       <c r="J90" s="2">
         <v>-1</v>
@@ -89366,7 +89378,7 @@
         <v>23</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>3956</v>
+        <v>3958</v>
       </c>
       <c r="F91" s="2">
         <v>13</v>
@@ -89375,10 +89387,10 @@
         <v>13</v>
       </c>
       <c r="H91" s="20" t="s">
-        <v>3950</v>
+        <v>3952</v>
       </c>
       <c r="I91" s="22" t="s">
-        <v>3957</v>
+        <v>3959</v>
       </c>
       <c r="J91" s="2">
         <v>-1</v>
@@ -89410,7 +89422,7 @@
         <v>24</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>3958</v>
+        <v>3960</v>
       </c>
       <c r="F92" s="2">
         <v>13</v>
@@ -89419,10 +89431,10 @@
         <v>13</v>
       </c>
       <c r="H92" s="20" t="s">
-        <v>3950</v>
+        <v>3952</v>
       </c>
       <c r="I92" s="22" t="s">
-        <v>3959</v>
+        <v>3961</v>
       </c>
       <c r="J92" s="2">
         <v>-1</v>
@@ -89454,7 +89466,7 @@
         <v>25</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>3960</v>
+        <v>3962</v>
       </c>
       <c r="F93" s="2">
         <v>13</v>
@@ -89463,10 +89475,10 @@
         <v>13</v>
       </c>
       <c r="H93" s="20" t="s">
-        <v>3950</v>
+        <v>3952</v>
       </c>
       <c r="I93" s="22" t="s">
-        <v>3961</v>
+        <v>3963</v>
       </c>
       <c r="J93" s="2">
         <v>-1</v>
@@ -89498,7 +89510,7 @@
         <v>26</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>3962</v>
+        <v>3964</v>
       </c>
       <c r="F94" s="2">
         <v>13</v>
@@ -89507,10 +89519,10 @@
         <v>13</v>
       </c>
       <c r="H94" s="20" t="s">
-        <v>3950</v>
+        <v>3965</v>
       </c>
       <c r="I94" s="22" t="s">
-        <v>3963</v>
+        <v>3966</v>
       </c>
       <c r="J94" s="2">
         <v>-1</v>
@@ -89548,7 +89560,7 @@
         <v>1</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>3964</v>
+        <v>3967</v>
       </c>
       <c r="F97" s="2">
         <v>14</v>
@@ -89557,10 +89569,10 @@
         <v>14</v>
       </c>
       <c r="H97" s="20" t="s">
-        <v>3965</v>
+        <v>3968</v>
       </c>
       <c r="I97" s="20" t="s">
-        <v>3966</v>
+        <v>3969</v>
       </c>
       <c r="J97" s="2">
         <v>-1</v>
@@ -89592,7 +89604,7 @@
         <v>2</v>
       </c>
       <c r="E98" s="2" t="s">
-        <v>3967</v>
+        <v>3970</v>
       </c>
       <c r="F98" s="2">
         <v>14</v>
@@ -89601,10 +89613,10 @@
         <v>14</v>
       </c>
       <c r="H98" s="20" t="s">
-        <v>3965</v>
+        <v>3968</v>
       </c>
       <c r="I98" s="20" t="s">
-        <v>3968</v>
+        <v>3971</v>
       </c>
       <c r="J98" s="2">
         <v>-1</v>
@@ -89636,7 +89648,7 @@
         <v>3</v>
       </c>
       <c r="E99" s="2" t="s">
-        <v>3969</v>
+        <v>3972</v>
       </c>
       <c r="F99" s="2">
         <v>14</v>
@@ -89645,10 +89657,10 @@
         <v>14</v>
       </c>
       <c r="H99" s="20" t="s">
-        <v>3965</v>
+        <v>3968</v>
       </c>
       <c r="I99" s="20" t="s">
-        <v>3970</v>
+        <v>3973</v>
       </c>
       <c r="J99" s="2">
         <v>-1</v>
@@ -89680,7 +89692,7 @@
         <v>4</v>
       </c>
       <c r="E100" s="2" t="s">
-        <v>3971</v>
+        <v>3974</v>
       </c>
       <c r="F100" s="2">
         <v>14</v>
@@ -89689,10 +89701,10 @@
         <v>14</v>
       </c>
       <c r="H100" s="20" t="s">
-        <v>3965</v>
+        <v>3968</v>
       </c>
       <c r="I100" s="20" t="s">
-        <v>3972</v>
+        <v>3975</v>
       </c>
       <c r="J100" s="2">
         <v>-1</v>
@@ -89724,7 +89736,7 @@
         <v>5</v>
       </c>
       <c r="E101" s="2" t="s">
-        <v>3973</v>
+        <v>3976</v>
       </c>
       <c r="F101" s="2">
         <v>14</v>
@@ -89733,10 +89745,10 @@
         <v>14</v>
       </c>
       <c r="H101" s="20" t="s">
-        <v>3965</v>
+        <v>3968</v>
       </c>
       <c r="I101" s="20" t="s">
-        <v>3974</v>
+        <v>3977</v>
       </c>
       <c r="J101" s="2">
         <v>-1</v>
@@ -89768,7 +89780,7 @@
         <v>6</v>
       </c>
       <c r="E102" s="2" t="s">
-        <v>3975</v>
+        <v>3978</v>
       </c>
       <c r="F102" s="2">
         <v>14</v>
@@ -89777,10 +89789,10 @@
         <v>14</v>
       </c>
       <c r="H102" s="20" t="s">
-        <v>3965</v>
+        <v>3968</v>
       </c>
       <c r="I102" s="20" t="s">
-        <v>3976</v>
+        <v>3979</v>
       </c>
       <c r="J102" s="2">
         <v>-1</v>
@@ -89812,7 +89824,7 @@
         <v>7</v>
       </c>
       <c r="E103" s="2" t="s">
-        <v>3977</v>
+        <v>3980</v>
       </c>
       <c r="F103" s="2">
         <v>14</v>
@@ -89821,10 +89833,10 @@
         <v>14</v>
       </c>
       <c r="H103" s="20" t="s">
-        <v>3965</v>
+        <v>3968</v>
       </c>
       <c r="I103" s="20" t="s">
-        <v>3978</v>
+        <v>3981</v>
       </c>
       <c r="J103" s="2">
         <v>-1</v>
@@ -89856,7 +89868,7 @@
         <v>8</v>
       </c>
       <c r="E104" s="2" t="s">
-        <v>3979</v>
+        <v>3982</v>
       </c>
       <c r="F104" s="2">
         <v>14</v>
@@ -89865,10 +89877,10 @@
         <v>14</v>
       </c>
       <c r="H104" s="20" t="s">
-        <v>3965</v>
+        <v>3968</v>
       </c>
       <c r="I104" s="20" t="s">
-        <v>3980</v>
+        <v>3983</v>
       </c>
       <c r="J104" s="2">
         <v>-1</v>
@@ -89900,7 +89912,7 @@
         <v>9</v>
       </c>
       <c r="E105" s="2" t="s">
-        <v>3981</v>
+        <v>3984</v>
       </c>
       <c r="F105" s="2">
         <v>14</v>
@@ -89909,10 +89921,10 @@
         <v>14</v>
       </c>
       <c r="H105" s="20" t="s">
-        <v>3965</v>
+        <v>3968</v>
       </c>
       <c r="I105" s="20" t="s">
-        <v>3982</v>
+        <v>3985</v>
       </c>
       <c r="J105" s="2">
         <v>-1</v>
@@ -89944,7 +89956,7 @@
         <v>10</v>
       </c>
       <c r="E106" s="2" t="s">
-        <v>3983</v>
+        <v>3986</v>
       </c>
       <c r="F106" s="2">
         <v>14</v>
@@ -89953,10 +89965,10 @@
         <v>14</v>
       </c>
       <c r="H106" s="20" t="s">
-        <v>3965</v>
+        <v>3968</v>
       </c>
       <c r="I106" s="20" t="s">
-        <v>3984</v>
+        <v>3987</v>
       </c>
       <c r="J106" s="2">
         <v>-1</v>
@@ -89988,7 +90000,7 @@
         <v>11</v>
       </c>
       <c r="E107" s="2" t="s">
-        <v>3985</v>
+        <v>3988</v>
       </c>
       <c r="F107" s="2">
         <v>14</v>
@@ -89997,10 +90009,10 @@
         <v>14</v>
       </c>
       <c r="H107" s="20" t="s">
-        <v>3965</v>
+        <v>3968</v>
       </c>
       <c r="I107" s="20" t="s">
-        <v>3986</v>
+        <v>3989</v>
       </c>
       <c r="J107" s="2">
         <v>-1</v>
@@ -90032,7 +90044,7 @@
         <v>12</v>
       </c>
       <c r="E108" s="2" t="s">
-        <v>3987</v>
+        <v>3990</v>
       </c>
       <c r="F108" s="2">
         <v>14</v>
@@ -90041,10 +90053,10 @@
         <v>14</v>
       </c>
       <c r="H108" s="20" t="s">
-        <v>3965</v>
+        <v>3968</v>
       </c>
       <c r="I108" s="20" t="s">
-        <v>3988</v>
+        <v>3991</v>
       </c>
       <c r="J108" s="2">
         <v>-1</v>
@@ -90076,7 +90088,7 @@
         <v>13</v>
       </c>
       <c r="E109" s="2" t="s">
-        <v>3989</v>
+        <v>3992</v>
       </c>
       <c r="F109" s="2">
         <v>14</v>
@@ -90085,10 +90097,10 @@
         <v>14</v>
       </c>
       <c r="H109" s="20" t="s">
-        <v>3965</v>
+        <v>3968</v>
       </c>
       <c r="I109" s="20" t="s">
-        <v>3990</v>
+        <v>3993</v>
       </c>
       <c r="J109" s="2">
         <v>-1</v>
@@ -90120,7 +90132,7 @@
         <v>14</v>
       </c>
       <c r="E110" s="2" t="s">
-        <v>3991</v>
+        <v>3994</v>
       </c>
       <c r="F110" s="2">
         <v>14</v>
@@ -90129,10 +90141,10 @@
         <v>14</v>
       </c>
       <c r="H110" s="20" t="s">
-        <v>3965</v>
+        <v>3968</v>
       </c>
       <c r="I110" s="20" t="s">
-        <v>3992</v>
+        <v>3995</v>
       </c>
       <c r="J110" s="2">
         <v>-1</v>
@@ -90164,7 +90176,7 @@
         <v>15</v>
       </c>
       <c r="E111" s="2" t="s">
-        <v>3993</v>
+        <v>3996</v>
       </c>
       <c r="F111" s="2">
         <v>14</v>
@@ -90173,10 +90185,10 @@
         <v>14</v>
       </c>
       <c r="H111" s="20" t="s">
-        <v>3965</v>
+        <v>3968</v>
       </c>
       <c r="I111" s="20" t="s">
-        <v>3994</v>
+        <v>3997</v>
       </c>
       <c r="J111" s="2">
         <v>-1</v>
@@ -90208,7 +90220,7 @@
         <v>16</v>
       </c>
       <c r="E112" s="2" t="s">
-        <v>3995</v>
+        <v>3998</v>
       </c>
       <c r="F112" s="2">
         <v>14</v>
@@ -90217,10 +90229,10 @@
         <v>14</v>
       </c>
       <c r="H112" s="20" t="s">
-        <v>3965</v>
+        <v>3968</v>
       </c>
       <c r="I112" s="20" t="s">
-        <v>3996</v>
+        <v>3999</v>
       </c>
       <c r="J112" s="2">
         <v>-1</v>
@@ -90252,7 +90264,7 @@
         <v>17</v>
       </c>
       <c r="E113" s="2" t="s">
-        <v>3997</v>
+        <v>4000</v>
       </c>
       <c r="F113" s="2">
         <v>14</v>
@@ -90261,10 +90273,10 @@
         <v>14</v>
       </c>
       <c r="H113" s="20" t="s">
-        <v>3965</v>
+        <v>3968</v>
       </c>
       <c r="I113" s="20" t="s">
-        <v>3998</v>
+        <v>4001</v>
       </c>
       <c r="J113" s="2">
         <v>-1</v>
@@ -90296,7 +90308,7 @@
         <v>18</v>
       </c>
       <c r="E114" s="2" t="s">
-        <v>3999</v>
+        <v>4002</v>
       </c>
       <c r="F114" s="2">
         <v>14</v>
@@ -90305,10 +90317,10 @@
         <v>14</v>
       </c>
       <c r="H114" s="20" t="s">
-        <v>3965</v>
+        <v>3968</v>
       </c>
       <c r="I114" s="20" t="s">
-        <v>4000</v>
+        <v>4003</v>
       </c>
       <c r="J114" s="2">
         <v>-1</v>
@@ -90340,7 +90352,7 @@
         <v>19</v>
       </c>
       <c r="E115" s="2" t="s">
-        <v>4001</v>
+        <v>4004</v>
       </c>
       <c r="F115" s="2">
         <v>14</v>
@@ -90349,10 +90361,10 @@
         <v>14</v>
       </c>
       <c r="H115" s="20" t="s">
-        <v>3965</v>
+        <v>3968</v>
       </c>
       <c r="I115" s="20" t="s">
-        <v>4002</v>
+        <v>4005</v>
       </c>
       <c r="J115" s="2">
         <v>-1</v>
@@ -90384,7 +90396,7 @@
         <v>20</v>
       </c>
       <c r="E116" s="2" t="s">
-        <v>4003</v>
+        <v>4006</v>
       </c>
       <c r="F116" s="2">
         <v>14</v>
@@ -90393,10 +90405,10 @@
         <v>14</v>
       </c>
       <c r="H116" s="20" t="s">
-        <v>4004</v>
+        <v>4007</v>
       </c>
       <c r="I116" s="20" t="s">
-        <v>4005</v>
+        <v>4008</v>
       </c>
       <c r="J116" s="2">
         <v>-1</v>
@@ -90428,7 +90440,7 @@
         <v>21</v>
       </c>
       <c r="E117" s="2" t="s">
-        <v>4006</v>
+        <v>4009</v>
       </c>
       <c r="F117" s="2">
         <v>14</v>
@@ -90437,10 +90449,10 @@
         <v>14</v>
       </c>
       <c r="H117" s="20" t="s">
-        <v>4004</v>
+        <v>4007</v>
       </c>
       <c r="I117" s="20" t="s">
-        <v>4007</v>
+        <v>4010</v>
       </c>
       <c r="J117" s="2">
         <v>-1</v>
@@ -90472,7 +90484,7 @@
         <v>22</v>
       </c>
       <c r="E118" s="2" t="s">
-        <v>4008</v>
+        <v>4011</v>
       </c>
       <c r="F118" s="2">
         <v>14</v>
@@ -90481,10 +90493,10 @@
         <v>14</v>
       </c>
       <c r="H118" s="20" t="s">
-        <v>4009</v>
+        <v>4012</v>
       </c>
       <c r="I118" s="20" t="s">
-        <v>4010</v>
+        <v>4013</v>
       </c>
       <c r="J118" s="2">
         <v>-1</v>
@@ -90516,7 +90528,7 @@
         <v>23</v>
       </c>
       <c r="E119" s="2" t="s">
-        <v>4011</v>
+        <v>4014</v>
       </c>
       <c r="F119" s="2">
         <v>14</v>
@@ -90525,10 +90537,10 @@
         <v>14</v>
       </c>
       <c r="H119" s="20" t="s">
-        <v>4012</v>
+        <v>4015</v>
       </c>
       <c r="I119" s="20" t="s">
-        <v>4013</v>
+        <v>4016</v>
       </c>
       <c r="J119" s="2">
         <v>-1</v>
@@ -90560,7 +90572,7 @@
         <v>24</v>
       </c>
       <c r="E120" s="2" t="s">
-        <v>4014</v>
+        <v>4017</v>
       </c>
       <c r="F120" s="2">
         <v>14</v>
@@ -90569,10 +90581,10 @@
         <v>14</v>
       </c>
       <c r="H120" s="20" t="s">
-        <v>4012</v>
+        <v>4015</v>
       </c>
       <c r="I120" s="20" t="s">
-        <v>4015</v>
+        <v>4018</v>
       </c>
       <c r="J120" s="2">
         <v>-1</v>
@@ -90604,7 +90616,7 @@
         <v>25</v>
       </c>
       <c r="E121" s="2" t="s">
-        <v>4016</v>
+        <v>4019</v>
       </c>
       <c r="F121" s="2">
         <v>14</v>
@@ -90613,10 +90625,10 @@
         <v>14</v>
       </c>
       <c r="H121" s="20" t="s">
-        <v>4012</v>
+        <v>4015</v>
       </c>
       <c r="I121" s="20" t="s">
-        <v>4017</v>
+        <v>4020</v>
       </c>
       <c r="J121" s="2">
         <v>-1</v>
@@ -90648,7 +90660,7 @@
         <v>26</v>
       </c>
       <c r="E122" s="2" t="s">
-        <v>4018</v>
+        <v>4021</v>
       </c>
       <c r="F122" s="2">
         <v>14</v>
@@ -90657,10 +90669,10 @@
         <v>14</v>
       </c>
       <c r="H122" s="20" t="s">
-        <v>4012</v>
+        <v>4022</v>
       </c>
       <c r="I122" s="20" t="s">
-        <v>4019</v>
+        <v>4023</v>
       </c>
       <c r="J122" s="2">
         <v>-1</v>

--- a/Excel/EquipConfig.xlsx
+++ b/Excel/EquipConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowHeight="17680" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="老版本" sheetId="7" r:id="rId1"/>
@@ -4998,7 +4998,7 @@
     <t>新手靴</t>
   </si>
   <si>
-    <t>斗笠一阶</t>
+    <t>斗笠</t>
   </si>
   <si>
     <t>26,27,28,12</t>
@@ -5166,7 +5166,7 @@
     <t>3000,3000,3000,3000,120,800,1</t>
   </si>
   <si>
-    <t>护盾一阶</t>
+    <t>护盾</t>
   </si>
   <si>
     <t>15,16,13</t>
@@ -5331,7 +5331,7 @@
     <t>3000,3000,3000,60,120,800,1</t>
   </si>
   <si>
-    <t>神符一阶</t>
+    <t>神符</t>
   </si>
   <si>
     <t>7,8,14,18,20</t>
@@ -5496,7 +5496,7 @@
     <t>300,100,3000,3000,3000,120,1</t>
   </si>
   <si>
-    <t>魔石一阶</t>
+    <t>魔石</t>
   </si>
   <si>
     <t>10,15,23</t>
@@ -10468,7 +10468,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A3:P391"/>
-  <sheetFormatPr defaultColWidth="13" defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultColWidth="13" defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="6.125" style="33" customWidth="1"/>
     <col min="2" max="2" width="6.5" style="33" customWidth="1"/>
@@ -26453,11 +26453,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="389" customFormat="1" ht="14.25" spans="4:4">
+    <row r="389" customFormat="1" ht="14" spans="4:4">
       <c r="D389" s="33"/>
     </row>
-    <row r="390" customFormat="1" ht="14.25"/>
-    <row r="391" customFormat="1" ht="14.25"/>
+    <row r="390" customFormat="1" ht="14"/>
+    <row r="391" customFormat="1" ht="14"/>
   </sheetData>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:G5 N3:P5" errorStyle="warning">

--- a/Excel/EquipConfig.xlsx
+++ b/Excel/EquipConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="11775" activeTab="3"/>
+    <workbookView windowHeight="17680" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="老版本" sheetId="7" r:id="rId1"/>
@@ -5169,25 +5169,25 @@
     <t>斗笠二七阶</t>
   </si>
   <si>
-    <t>4000,4000,4000,4000,140,1000,2</t>
+    <t>4000,4000,4000,3600,140,1000,2</t>
   </si>
   <si>
     <t>斗笠二八阶</t>
   </si>
   <si>
-    <t>5000,5000,5000,5000,160,1200,3</t>
+    <t>5000,5000,5000,4200,160,1200,3</t>
   </si>
   <si>
     <t>斗笠二九阶</t>
   </si>
   <si>
-    <t>6500,6500,6500,6500,180,1400,4</t>
+    <t>6500,6500,6500,4800,180,1400,4</t>
   </si>
   <si>
     <t>斗笠三十阶</t>
   </si>
   <si>
-    <t>8000,8000,8000,8000,200,1600,5</t>
+    <t>8000,8000,8000,5400,200,1600,5</t>
   </si>
   <si>
     <t>护盾一阶</t>
@@ -5358,25 +5358,25 @@
     <t>护盾二七阶</t>
   </si>
   <si>
-    <t>4000,4000,4000,70,140,1000,2</t>
+    <t>4000,4000,3600,70,140,1000,2</t>
   </si>
   <si>
     <t>护盾二八阶</t>
   </si>
   <si>
-    <t>5000,5000,5000,80,160,1200,3</t>
+    <t>5000,5000,4200,80,160,1200,3</t>
   </si>
   <si>
     <t>护盾二九阶</t>
   </si>
   <si>
-    <t>6500,6500,6500,90,180,1400,4</t>
+    <t>6500,6500,4800,90,180,1400,4</t>
   </si>
   <si>
     <t>护盾三十阶</t>
   </si>
   <si>
-    <t>8000,8000,8000,100,200,1600,5</t>
+    <t>8000,8000,5400,100,200,1600,5</t>
   </si>
   <si>
     <t>神符一阶</t>
@@ -5547,25 +5547,25 @@
     <t>神符二七阶</t>
   </si>
   <si>
-    <t>360,110,4000,4000,4000,140,2</t>
+    <t>360,120,4000,4000,4000,140,2</t>
   </si>
   <si>
     <t>神符二八阶</t>
   </si>
   <si>
-    <t>420,120,5000,5000,5000,160,3</t>
+    <t>420,140,5000,5000,5000,160,3</t>
   </si>
   <si>
     <t>神符二九阶</t>
   </si>
   <si>
-    <t>480,140,6500,6500,6500,180,4</t>
+    <t>480,160,6500,6500,6500,180,4</t>
   </si>
   <si>
     <t>神符三十阶</t>
   </si>
   <si>
-    <t>540,160,8000,8000,8000,200,5</t>
+    <t>540,180,8000,8000,8000,200,5</t>
   </si>
   <si>
     <t>魔石一阶</t>
@@ -5742,25 +5742,25 @@
     <t>魔石二七阶</t>
   </si>
   <si>
-    <t>110,4000,6,240,240,1000,2</t>
+    <t>120,4000,6,240,240,1000,2</t>
   </si>
   <si>
     <t>魔石二八阶</t>
   </si>
   <si>
-    <t>120,5000,6,280,280,1200,3</t>
+    <t>140,5000,6,280,280,1200,3</t>
   </si>
   <si>
     <t>魔石二九阶</t>
   </si>
   <si>
-    <t>130,5000,6,320,320,1400,4</t>
+    <t>160,5000,6,320,320,1400,4</t>
   </si>
   <si>
     <t>魔石三十阶</t>
   </si>
   <si>
-    <t>140,5000,6,360,360,1600,5</t>
+    <t>180,5000,6,360,360,1600,5</t>
   </si>
   <si>
     <t>21000601</t>
@@ -9692,12 +9692,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -10564,7 +10564,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A3:P391"/>
-  <sheetFormatPr defaultColWidth="13" defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultColWidth="13" defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="6.125" style="33" customWidth="1"/>
     <col min="2" max="2" width="6.5" style="33" customWidth="1"/>
@@ -26549,11 +26549,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="389" customFormat="1" ht="14.25" spans="4:4">
+    <row r="389" customFormat="1" ht="14" spans="4:4">
       <c r="D389" s="33"/>
     </row>
-    <row r="390" customFormat="1" ht="14.25"/>
-    <row r="391" customFormat="1" ht="14.25"/>
+    <row r="390" customFormat="1" ht="14"/>
+    <row r="391" customFormat="1" ht="14"/>
   </sheetData>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:G5 N3:P5" errorStyle="warning">

--- a/Excel/EquipConfig.xlsx
+++ b/Excel/EquipConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375" activeTab="2"/>
+    <workbookView windowHeight="17680" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="老版本" sheetId="7" r:id="rId1"/>
@@ -9941,12 +9941,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -10813,7 +10813,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A3:P391"/>
-  <sheetFormatPr defaultColWidth="13" defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultColWidth="13" defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="6.125" style="33" customWidth="1"/>
     <col min="2" max="2" width="6.5" style="33" customWidth="1"/>
@@ -26798,11 +26798,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="389" customFormat="1" ht="14.25" spans="4:4">
+    <row r="389" customFormat="1" ht="14" spans="4:4">
       <c r="D389" s="33"/>
     </row>
-    <row r="390" customFormat="1" ht="14.25"/>
-    <row r="391" customFormat="1" ht="14.25"/>
+    <row r="390" customFormat="1" ht="14"/>
+    <row r="391" customFormat="1" ht="14"/>
   </sheetData>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:G5 N3:P5" errorStyle="warning">
@@ -38910,7 +38910,7 @@
     </row>
     <row r="288" s="27" customFormat="1" customHeight="1" spans="3:16">
       <c r="C288" s="27">
-        <v>21020020</v>
+        <v>21020010</v>
       </c>
       <c r="D288" s="27">
         <v>1450</v>
@@ -39262,7 +39262,7 @@
     </row>
     <row r="296" s="27" customFormat="1" customHeight="1" spans="3:16">
       <c r="C296" s="27">
-        <v>22020020</v>
+        <v>22020010</v>
       </c>
       <c r="D296" s="27">
         <v>1450</v>
@@ -39614,7 +39614,7 @@
     </row>
     <row r="304" s="27" customFormat="1" customHeight="1" spans="3:16">
       <c r="C304" s="27">
-        <v>23020020</v>
+        <v>23020010</v>
       </c>
       <c r="D304" s="27">
         <v>1450</v>

--- a/Excel/EquipConfig.xlsx
+++ b/Excel/EquipConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680" activeTab="1"/>
+    <workbookView windowWidth="27945" windowHeight="12375" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="老版本" sheetId="7" r:id="rId1"/>
@@ -10813,7 +10813,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A3:P391"/>
-  <sheetFormatPr defaultColWidth="13" defaultRowHeight="13"/>
+  <sheetFormatPr defaultColWidth="13" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="6.125" style="33" customWidth="1"/>
     <col min="2" max="2" width="6.5" style="33" customWidth="1"/>
@@ -26798,11 +26798,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="389" customFormat="1" ht="14" spans="4:4">
+    <row r="389" customFormat="1" ht="14.25" spans="4:4">
       <c r="D389" s="33"/>
     </row>
-    <row r="390" customFormat="1" ht="14"/>
-    <row r="391" customFormat="1" ht="14"/>
+    <row r="390" customFormat="1" ht="14.25"/>
+    <row r="391" customFormat="1" ht="14.25"/>
   </sheetData>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:G5 N3:P5" errorStyle="warning">

--- a/Excel/EquipConfig.xlsx
+++ b/Excel/EquipConfig.xlsx
@@ -9941,12 +9941,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -41989,7 +41989,7 @@
         <v>28</v>
       </c>
       <c r="P56" s="27">
-        <v>4019</v>
+        <v>4026</v>
       </c>
     </row>
     <row r="57" s="18" customFormat="1" customHeight="1" spans="3:16">
@@ -42033,7 +42033,7 @@
         <v>28</v>
       </c>
       <c r="P57" s="27">
-        <v>4019</v>
+        <v>4026</v>
       </c>
     </row>
     <row r="58" s="18" customFormat="1" customHeight="1" spans="3:16">
@@ -42077,7 +42077,7 @@
         <v>28</v>
       </c>
       <c r="P58" s="27">
-        <v>4019</v>
+        <v>4026</v>
       </c>
     </row>
     <row r="59" s="18" customFormat="1" customHeight="1" spans="3:16">
@@ -42121,7 +42121,7 @@
         <v>28</v>
       </c>
       <c r="P59" s="27">
-        <v>4019</v>
+        <v>4026</v>
       </c>
     </row>
     <row r="60" s="18" customFormat="1" customHeight="1" spans="3:16">
@@ -42165,7 +42165,7 @@
         <v>28</v>
       </c>
       <c r="P60" s="27">
-        <v>4019</v>
+        <v>4026</v>
       </c>
     </row>
     <row r="61" s="18" customFormat="1" customHeight="1" spans="3:16">
@@ -42209,7 +42209,7 @@
         <v>28</v>
       </c>
       <c r="P61" s="27">
-        <v>4019</v>
+        <v>4026</v>
       </c>
     </row>
     <row r="62" s="18" customFormat="1" customHeight="1" spans="3:16">
@@ -42253,7 +42253,7 @@
         <v>28</v>
       </c>
       <c r="P62" s="27">
-        <v>4019</v>
+        <v>4026</v>
       </c>
     </row>
     <row r="63" s="18" customFormat="1" customHeight="1" spans="3:16">
@@ -42297,7 +42297,7 @@
         <v>28</v>
       </c>
       <c r="P63" s="27">
-        <v>4019</v>
+        <v>4026</v>
       </c>
     </row>
     <row r="64" s="18" customFormat="1" customHeight="1" spans="3:16">
@@ -42341,7 +42341,7 @@
         <v>29</v>
       </c>
       <c r="P64" s="27">
-        <v>4019</v>
+        <v>4026</v>
       </c>
     </row>
     <row r="65" s="18" customFormat="1" customHeight="1" spans="3:16">
@@ -42385,7 +42385,7 @@
         <v>29</v>
       </c>
       <c r="P65" s="27">
-        <v>4019</v>
+        <v>4026</v>
       </c>
     </row>
     <row r="66" s="18" customFormat="1" customHeight="1" spans="3:16">
@@ -42429,7 +42429,7 @@
         <v>29</v>
       </c>
       <c r="P66" s="27">
-        <v>4019</v>
+        <v>4026</v>
       </c>
     </row>
     <row r="67" s="18" customFormat="1" customHeight="1" spans="3:16">
@@ -42473,7 +42473,7 @@
         <v>29</v>
       </c>
       <c r="P67" s="27">
-        <v>4019</v>
+        <v>4026</v>
       </c>
     </row>
     <row r="68" s="18" customFormat="1" customHeight="1" spans="3:16">
@@ -42517,7 +42517,7 @@
         <v>29</v>
       </c>
       <c r="P68" s="27">
-        <v>4019</v>
+        <v>4026</v>
       </c>
     </row>
     <row r="69" s="18" customFormat="1" customHeight="1" spans="3:16">
@@ -42561,7 +42561,7 @@
         <v>29</v>
       </c>
       <c r="P69" s="27">
-        <v>4019</v>
+        <v>4026</v>
       </c>
     </row>
     <row r="70" s="18" customFormat="1" customHeight="1" spans="3:16">
@@ -42605,7 +42605,7 @@
         <v>29</v>
       </c>
       <c r="P70" s="27">
-        <v>4019</v>
+        <v>4026</v>
       </c>
     </row>
     <row r="71" s="18" customFormat="1" customHeight="1" spans="3:16">
@@ -42649,7 +42649,7 @@
         <v>29</v>
       </c>
       <c r="P71" s="27">
-        <v>4019</v>
+        <v>4026</v>
       </c>
     </row>
     <row r="72" s="18" customFormat="1" customHeight="1" spans="3:16">
@@ -42693,7 +42693,7 @@
         <v>137</v>
       </c>
       <c r="P72" s="27">
-        <v>4019</v>
+        <v>4026</v>
       </c>
     </row>
     <row r="73" s="18" customFormat="1" customHeight="1" spans="3:16">
@@ -42737,7 +42737,7 @@
         <v>137</v>
       </c>
       <c r="P73" s="27">
-        <v>4019</v>
+        <v>4026</v>
       </c>
     </row>
     <row r="74" s="18" customFormat="1" customHeight="1" spans="3:16">
@@ -42781,7 +42781,7 @@
         <v>137</v>
       </c>
       <c r="P74" s="27">
-        <v>4019</v>
+        <v>4026</v>
       </c>
     </row>
     <row r="75" s="18" customFormat="1" customHeight="1" spans="3:16">
@@ -42825,7 +42825,7 @@
         <v>137</v>
       </c>
       <c r="P75" s="27">
-        <v>4019</v>
+        <v>4026</v>
       </c>
     </row>
     <row r="76" s="18" customFormat="1" customHeight="1" spans="3:16">
@@ -42869,7 +42869,7 @@
         <v>137</v>
       </c>
       <c r="P76" s="27">
-        <v>4019</v>
+        <v>4026</v>
       </c>
     </row>
     <row r="77" s="18" customFormat="1" customHeight="1" spans="3:16">
@@ -42913,7 +42913,7 @@
         <v>137</v>
       </c>
       <c r="P77" s="27">
-        <v>4019</v>
+        <v>4026</v>
       </c>
     </row>
     <row r="78" s="18" customFormat="1" customHeight="1" spans="3:16">
@@ -42957,7 +42957,7 @@
         <v>137</v>
       </c>
       <c r="P78" s="27">
-        <v>4019</v>
+        <v>4026</v>
       </c>
     </row>
     <row r="79" s="18" customFormat="1" customHeight="1" spans="3:16">
@@ -43001,7 +43001,7 @@
         <v>137</v>
       </c>
       <c r="P79" s="27">
-        <v>4019</v>
+        <v>4026</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/EquipConfig.xlsx
+++ b/Excel/EquipConfig.xlsx
@@ -9923,12 +9923,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -45243,7 +45243,7 @@
         <v>29</v>
       </c>
       <c r="Q81" s="24">
-        <v>4027</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82" s="24" customFormat="1" customHeight="1" spans="3:17">
@@ -45290,7 +45290,7 @@
         <v>29</v>
       </c>
       <c r="Q82" s="24">
-        <v>4027</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83" s="24" customFormat="1" customHeight="1" spans="3:17">
@@ -45337,7 +45337,7 @@
         <v>29</v>
       </c>
       <c r="Q83" s="24">
-        <v>4027</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84" s="24" customFormat="1" customHeight="1" spans="3:17">
@@ -45384,7 +45384,7 @@
         <v>29</v>
       </c>
       <c r="Q84" s="24">
-        <v>4027</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85" s="24" customFormat="1" customHeight="1" spans="3:17">
@@ -45431,7 +45431,7 @@
         <v>29</v>
       </c>
       <c r="Q85" s="24">
-        <v>4027</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86" s="24" customFormat="1" customHeight="1" spans="3:17">
@@ -45478,7 +45478,7 @@
         <v>29</v>
       </c>
       <c r="Q86" s="24">
-        <v>4027</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87" s="24" customFormat="1" customHeight="1" spans="3:17">
@@ -45525,7 +45525,7 @@
         <v>29</v>
       </c>
       <c r="Q87" s="24">
-        <v>4027</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88" s="24" customFormat="1" customHeight="1" spans="3:17">
@@ -45572,7 +45572,7 @@
         <v>29</v>
       </c>
       <c r="Q88" s="24">
-        <v>4027</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89" s="24" customFormat="1" customHeight="1" spans="3:17">
@@ -45619,7 +45619,7 @@
         <v>30</v>
       </c>
       <c r="Q89" s="24">
-        <v>4027</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90" s="24" customFormat="1" customHeight="1" spans="3:17">
@@ -45666,7 +45666,7 @@
         <v>30</v>
       </c>
       <c r="Q90" s="24">
-        <v>4027</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91" s="24" customFormat="1" customHeight="1" spans="3:17">
@@ -45713,7 +45713,7 @@
         <v>30</v>
       </c>
       <c r="Q91" s="24">
-        <v>4027</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92" s="24" customFormat="1" customHeight="1" spans="3:17">
@@ -45760,7 +45760,7 @@
         <v>30</v>
       </c>
       <c r="Q92" s="24">
-        <v>4027</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93" s="24" customFormat="1" customHeight="1" spans="3:17">
@@ -45807,7 +45807,7 @@
         <v>30</v>
       </c>
       <c r="Q93" s="24">
-        <v>4027</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94" s="24" customFormat="1" customHeight="1" spans="3:17">
@@ -45854,7 +45854,7 @@
         <v>30</v>
       </c>
       <c r="Q94" s="24">
-        <v>4027</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95" s="24" customFormat="1" customHeight="1" spans="3:17">
@@ -45901,7 +45901,7 @@
         <v>30</v>
       </c>
       <c r="Q95" s="24">
-        <v>4027</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96" s="24" customFormat="1" customHeight="1" spans="3:17">
@@ -45948,7 +45948,7 @@
         <v>30</v>
       </c>
       <c r="Q96" s="24">
-        <v>4027</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97" s="24" customFormat="1" customHeight="1" spans="3:17">
@@ -45995,7 +45995,7 @@
         <v>138</v>
       </c>
       <c r="Q97" s="24">
-        <v>4027</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98" s="24" customFormat="1" customHeight="1" spans="3:17">
@@ -46042,7 +46042,7 @@
         <v>138</v>
       </c>
       <c r="Q98" s="24">
-        <v>4027</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99" s="24" customFormat="1" customHeight="1" spans="3:17">
@@ -46089,7 +46089,7 @@
         <v>138</v>
       </c>
       <c r="Q99" s="24">
-        <v>4027</v>
+        <v>0</v>
       </c>
     </row>
     <row r="100" s="24" customFormat="1" customHeight="1" spans="3:17">
@@ -46136,7 +46136,7 @@
         <v>138</v>
       </c>
       <c r="Q100" s="24">
-        <v>4027</v>
+        <v>0</v>
       </c>
     </row>
     <row r="101" s="24" customFormat="1" customHeight="1" spans="3:17">
@@ -46183,7 +46183,7 @@
         <v>138</v>
       </c>
       <c r="Q101" s="24">
-        <v>4027</v>
+        <v>0</v>
       </c>
     </row>
     <row r="102" s="24" customFormat="1" customHeight="1" spans="3:17">
@@ -46230,7 +46230,7 @@
         <v>138</v>
       </c>
       <c r="Q102" s="24">
-        <v>4027</v>
+        <v>0</v>
       </c>
     </row>
     <row r="103" s="24" customFormat="1" customHeight="1" spans="3:17">
@@ -46277,7 +46277,7 @@
         <v>138</v>
       </c>
       <c r="Q103" s="24">
-        <v>4027</v>
+        <v>0</v>
       </c>
     </row>
     <row r="104" s="24" customFormat="1" customHeight="1" spans="3:17">
@@ -46324,7 +46324,7 @@
         <v>138</v>
       </c>
       <c r="Q104" s="24">
-        <v>4027</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
